--- a/download/Ассортимент_Олимп_300_SKU.xlsx
+++ b/download/Ассортимент_Олимп_300_SKU.xlsx
@@ -594,19 +594,21 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Стартовый ассортимент Олимп — 300 SKU</t>
+          <t>Стартовый ассортимент Олимп — 300 SKU (сбалансированный)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Отобрано из ABC-анализа продаж (Урал, 659 SKU) · База: MML + топ A-группа</t>
+          <t>ABC-анализ + прайс-лист · Убраны: СТРОЙКОМПЛЕКТ, EMPILS ЭКОНОМ, NoName · Добавлены: NEWTONE (14), AvantGarde (17)</t>
         </is>
       </c>
     </row>
@@ -630,7 +632,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Помещения</t>
+          <t>Помещения (интерьер)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -666,26 +668,26 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>23</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -699,21 +701,23 @@
         <v>6</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="F7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G7" s="10" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
     </row>
@@ -724,19 +728,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>34</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>300</v>
@@ -777,39 +781,35 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>AvantGarde</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
           <t>Расцвет</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Простокрашено! БАУ</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>PROFIWOOD</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>EMPILS ЭКОНОМ</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>СТРОЙКОМПЛЕКТ</t>
-        </is>
-      </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>NoName</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
           <t>ИТОГО</t>
         </is>
       </c>
+      <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -824,24 +824,19 @@
         <v>6</v>
       </c>
       <c r="D12" s="15" t="inlineStr"/>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>68</v>
-      </c>
-      <c r="G12" s="15" t="inlineStr"/>
       <c r="H12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>160</v>
+        <v>46</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr"/>
+      <c r="J12" s="7" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -858,19 +853,20 @@
         <v>29</v>
       </c>
       <c r="E13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="H13" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="15" t="inlineStr"/>
-      <c r="H13" s="15" t="inlineStr"/>
-      <c r="I13" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="15" t="inlineStr"/>
-      <c r="K13" s="7" t="n">
-        <v>61</v>
+      <c r="I13" s="15" t="inlineStr"/>
+      <c r="J13" s="7" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -882,20 +878,19 @@
       <c r="B14" s="15" t="inlineStr"/>
       <c r="C14" s="15" t="inlineStr"/>
       <c r="D14" s="15" t="inlineStr"/>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="15" t="inlineStr"/>
-      <c r="G14" s="19" t="n">
+      <c r="H14" s="15" t="inlineStr"/>
+      <c r="I14" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="H14" s="15" t="inlineStr"/>
-      <c r="I14" s="15" t="inlineStr"/>
-      <c r="J14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>44</v>
+      <c r="J14" s="7" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -909,17 +904,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="15" t="inlineStr"/>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr"/>
+      <c r="G15" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="H15" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="15" t="inlineStr"/>
-      <c r="H15" s="15" t="inlineStr"/>
       <c r="I15" s="15" t="inlineStr"/>
-      <c r="J15" s="15" t="inlineStr"/>
-      <c r="K15" s="7" t="n">
+      <c r="J15" s="7" t="n">
         <v>34</v>
       </c>
     </row>
@@ -932,16 +926,17 @@
       <c r="B16" s="15" t="inlineStr"/>
       <c r="C16" s="15" t="inlineStr"/>
       <c r="D16" s="15" t="inlineStr"/>
-      <c r="E16" s="15" t="inlineStr"/>
-      <c r="F16" s="15" t="inlineStr"/>
+      <c r="E16" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>2</v>
+      </c>
       <c r="G16" s="15" t="inlineStr"/>
       <c r="H16" s="15" t="inlineStr"/>
-      <c r="I16" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="15" t="inlineStr"/>
-      <c r="K16" s="7" t="n">
-        <v>1</v>
+      <c r="I16" s="15" t="inlineStr"/>
+      <c r="J16" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -960,52 +955,49 @@
         <v>29</v>
       </c>
       <c r="E17" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G17" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I17" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="H17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" s="24" t="n">
+      <c r="J17" s="24" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>ABC-АНАЛИЗ ОТОБРАННЫХ 300 SKU:</t>
+          <t>ABC-АНАЛИЗ 300 SKU:</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>Группа А: 132 SKU (44%) — топ-продавцы</t>
+          <t>Группа А: 123 SKU (41%) — топ-продавцы</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>Группа В: 96 SKU (32%) — средние</t>
+          <t>Группа В: 76 SKU (25%) — средние</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>Группа С: 72 SKU (24%) — хвост</t>
+          <t>Группа С: 101 SKU (34%) — хвост + новинки</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1022,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1040,7 +1032,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Стартовый ассортимент 300 SKU для Олимп</t>
+          <t>Стартовый ассортимент 300 SKU для Олимп (сбалансированный)</t>
         </is>
       </c>
     </row>
@@ -1330,25 +1322,25 @@
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>EMPILS ЭКОНОМ</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-эмаль ВДАК</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>Эмаль EMPILS ПФ-115 ЭКОНОМ чёрная 20 кг</t>
+          <t>Грунт-эмаль AvantGarde (база А) глянцевая белая</t>
         </is>
       </c>
       <c r="G10" s="27" t="n">
-        <v>7803</v>
+        <v>0</v>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -1368,25 +1360,25 @@
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>NoName</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Грунт-эмаль ВДАК</t>
         </is>
       </c>
       <c r="F11" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 белая 0.7 кг</t>
+          <t>Грунт-эмаль AvantGarde глянцевая зеленая RAL 6016</t>
         </is>
       </c>
       <c r="G11" s="27" t="n">
-        <v>79760</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -1406,25 +1398,25 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>NoName</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-эмаль ВДАК</t>
         </is>
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 синяя 0.7 кг</t>
+          <t>Грунт-эмаль AvantGarde глянцевая красно-коричневая RAL 8015</t>
         </is>
       </c>
       <c r="G12" s="27" t="n">
-        <v>79754</v>
+        <v>0</v>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -1444,25 +1436,25 @@
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>NoName</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-эмаль ВДАК</t>
         </is>
       </c>
       <c r="F13" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 чёрная 0.7 кг</t>
+          <t>Грунт-эмаль AvantGarde глянцевая серая RAL 7042</t>
         </is>
       </c>
       <c r="G13" s="27" t="n">
-        <v>79757</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -1482,25 +1474,25 @@
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>NoName</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-эмаль ВДАК</t>
         </is>
       </c>
       <c r="F14" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 ярко-жёлтая 0.7 кг</t>
+          <t>Грунт-эмаль AvantGarde глянцевая черная RAL 9005</t>
         </is>
       </c>
       <c r="G14" s="27" t="n">
-        <v>79758</v>
+        <v>0</v>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -1520,21 +1512,21 @@
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>ОРЕОЛ TITAN</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль быстросохнущая ОРЕОЛ TITAN матовая чёрная RAL 9005 0.75 л 0.9 кг</t>
+          <t>Эмаль AvantGarde (база А) глянцевая белая</t>
         </is>
       </c>
       <c r="G15" s="27" t="n">
-        <v>83777</v>
+        <v>0</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
@@ -1568,11 +1560,11 @@
       </c>
       <c r="F16" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль быстросохнущая ОРЕОЛ TITAN матовая чёрная RAL 9005 2.2 л 2.7 кг</t>
+          <t>Грунт-эмаль быстросохнущая ОРЕОЛ TITAN матовая чёрная RAL 9005 0.75 л 0.9 кг</t>
         </is>
       </c>
       <c r="G16" s="27" t="n">
-        <v>83779</v>
+        <v>83777</v>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
@@ -1606,11 +1598,11 @@
       </c>
       <c r="F17" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN белый RAL 9010 0.75 л 0.85 кг</t>
+          <t>Грунт-эмаль быстросохнущая ОРЕОЛ TITAN матовая чёрная RAL 9005 2.2 л 2.7 кг</t>
         </is>
       </c>
       <c r="G17" s="27" t="n">
-        <v>87269</v>
+        <v>83779</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
@@ -1644,11 +1636,11 @@
       </c>
       <c r="F18" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN белый RAL 9010 2 л 2.3 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN белый RAL 9010 0.75 л 0.85 кг</t>
         </is>
       </c>
       <c r="G18" s="27" t="n">
-        <v>87270</v>
+        <v>87269</v>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
@@ -1682,11 +1674,11 @@
       </c>
       <c r="F19" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN графитовый серый RAL 7024 0.75 л 0.8 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN белый RAL 9010 2 л 2.3 кг</t>
         </is>
       </c>
       <c r="G19" s="27" t="n">
-        <v>87286</v>
+        <v>87270</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
@@ -1720,11 +1712,11 @@
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN графитовый серый RAL 7024 2 л 2.2 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN графитовый серый RAL 7024 0.75 л 0.8 кг</t>
         </is>
       </c>
       <c r="G20" s="27" t="n">
-        <v>87287</v>
+        <v>87286</v>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
@@ -1758,15 +1750,15 @@
       </c>
       <c r="F21" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN серый RAL 7004 0.75 л 0.8 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN графитовый серый RAL 7024 2 л 2.2 кг</t>
         </is>
       </c>
       <c r="G21" s="27" t="n">
-        <v>87281</v>
+        <v>87287</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -1796,15 +1788,15 @@
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN серый RAL 7004 2 л 2 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN серый RAL 7004 0.75 л 0.8 кг</t>
         </is>
       </c>
       <c r="G22" s="27" t="n">
-        <v>87282</v>
+        <v>87281</v>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -1834,15 +1826,15 @@
       </c>
       <c r="F23" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN чёрный RAL 9005 0.75 л 0.75 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN серый RAL 7004 2 л 2 кг</t>
         </is>
       </c>
       <c r="G23" s="27" t="n">
-        <v>87289</v>
+        <v>87282</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -1872,15 +1864,15 @@
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN чёрный RAL 9005 2 л 2 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN чёрный RAL 9005 0.75 л 0.75 кг</t>
         </is>
       </c>
       <c r="G24" s="27" t="n">
-        <v>87290</v>
+        <v>87289</v>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -1910,11 +1902,11 @@
       </c>
       <c r="F25" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN шоколадно-коричневый RAL 8017 0.75 л 0.75 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN чёрный RAL 9005 2 л 2 кг</t>
         </is>
       </c>
       <c r="G25" s="27" t="n">
-        <v>87292</v>
+        <v>87290</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
@@ -1948,11 +1940,11 @@
       </c>
       <c r="F26" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN шоколадно-коричневый RAL 8017 2 л 2 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN шоколадно-коричневый RAL 8017 0.75 л 0.75 кг</t>
         </is>
       </c>
       <c r="G26" s="27" t="n">
-        <v>87293</v>
+        <v>87292</v>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
@@ -1981,16 +1973,16 @@
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F27" s="27" t="inlineStr">
         <is>
-          <t>Эмаль с молотковым эффектом ОРЕОЛ TITAN коричневая 0.8 кг</t>
+          <t>Грунт-эмаль по ржавчине ОРЕОЛ TITAN шоколадно-коричневый RAL 8017 2 л 2 кг</t>
         </is>
       </c>
       <c r="G27" s="27" t="n">
-        <v>77660</v>
+        <v>87293</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
@@ -2024,11 +2016,11 @@
       </c>
       <c r="F28" s="27" t="inlineStr">
         <is>
-          <t>Эмаль с молотковым эффектом ОРЕОЛ TITAN серебристая 0.8 кг</t>
+          <t>Эмаль с молотковым эффектом ОРЕОЛ TITAN коричневая 0.8 кг</t>
         </is>
       </c>
       <c r="G28" s="27" t="n">
-        <v>77642</v>
+        <v>77660</v>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
@@ -2062,11 +2054,11 @@
       </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
-          <t>Эмаль с молотковым эффектом ОРЕОЛ TITAN чёрная 0.8 кг</t>
+          <t>Эмаль с молотковым эффектом ОРЕОЛ TITAN серебристая 0.8 кг</t>
         </is>
       </c>
       <c r="G29" s="27" t="n">
-        <v>77636</v>
+        <v>77642</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
@@ -2090,25 +2082,25 @@
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>ОРЕОЛ TITAN</t>
         </is>
       </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F30" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" белая 0.8 кг</t>
+          <t>Эмаль с молотковым эффектом ОРЕОЛ TITAN чёрная 0.8 кг</t>
         </is>
       </c>
       <c r="G30" s="27" t="n">
-        <v>81302</v>
+        <v>77636</v>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -2138,11 +2130,11 @@
       </c>
       <c r="F31" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" белая 1.8 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" белая 0.8 кг</t>
         </is>
       </c>
       <c r="G31" s="27" t="n">
-        <v>85162</v>
+        <v>81302</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
@@ -2176,15 +2168,15 @@
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" белая 2.7 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" белая 1.8 кг</t>
         </is>
       </c>
       <c r="G32" s="27" t="n">
-        <v>69683</v>
+        <v>85162</v>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -2328,15 +2320,15 @@
       </c>
       <c r="F36" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" зелёная 2.7 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" красно-коричневая 0.8 кг</t>
         </is>
       </c>
       <c r="G36" s="27" t="n">
-        <v>69700</v>
+        <v>81303</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -2366,11 +2358,11 @@
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" красно-коричневая 0.8 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" серая 0.8 кг</t>
         </is>
       </c>
       <c r="G37" s="27" t="n">
-        <v>81303</v>
+        <v>81332</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
@@ -2404,11 +2396,11 @@
       </c>
       <c r="F38" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" серая 0.8 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" серая 1.8 кг</t>
         </is>
       </c>
       <c r="G38" s="27" t="n">
-        <v>81332</v>
+        <v>85167</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
@@ -2442,11 +2434,11 @@
       </c>
       <c r="F39" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" серая 1.8 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" серая 2.7 кг</t>
         </is>
       </c>
       <c r="G39" s="27" t="n">
-        <v>85167</v>
+        <v>69704</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
@@ -2480,11 +2472,11 @@
       </c>
       <c r="F40" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" серая 2.7 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" синяя 0.8 кг</t>
         </is>
       </c>
       <c r="G40" s="27" t="n">
-        <v>69704</v>
+        <v>81333</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
@@ -2518,15 +2510,15 @@
       </c>
       <c r="F41" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" серая 5 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" чёрная 0.8 кг</t>
         </is>
       </c>
       <c r="G41" s="27" t="n">
-        <v>70267</v>
+        <v>81334</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -2556,11 +2548,11 @@
       </c>
       <c r="F42" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" синяя 0.8 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" чёрная 1.8 кг</t>
         </is>
       </c>
       <c r="G42" s="27" t="n">
-        <v>81333</v>
+        <v>85169</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
@@ -2594,15 +2586,15 @@
       </c>
       <c r="F43" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" синяя 1.8 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" шоколадная 0.8 кг</t>
         </is>
       </c>
       <c r="G43" s="27" t="n">
-        <v>85168</v>
+        <v>81335</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -2632,11 +2624,11 @@
       </c>
       <c r="F44" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" чёрная 0.8 кг</t>
+          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" шоколадная 1.8 кг</t>
         </is>
       </c>
       <c r="G44" s="27" t="n">
-        <v>81334</v>
+        <v>85170</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
@@ -2665,20 +2657,20 @@
       </c>
       <c r="E45" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные для радиаторов</t>
         </is>
       </c>
       <c r="F45" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" чёрная 1.8 кг</t>
+          <t>Эмаль "ПРОСТОКРАШЕНО!" алкидная для радиаторов отопления 0.9 кг</t>
         </is>
       </c>
       <c r="G45" s="27" t="n">
-        <v>85169</v>
+        <v>86082</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2695,16 @@
       </c>
       <c r="E46" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F46" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" чёрная 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" бежевая БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G46" s="27" t="n">
-        <v>69712</v>
+        <v>81295</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
@@ -2741,20 +2733,20 @@
       </c>
       <c r="E47" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F47" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" чёрная 5 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" белая БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G47" s="27" t="n">
-        <v>70269</v>
+        <v>81277</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -2779,16 +2771,16 @@
       </c>
       <c r="E48" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F48" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" шоколадная 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" белая БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G48" s="27" t="n">
-        <v>81335</v>
+        <v>85171</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2817,16 +2809,16 @@
       </c>
       <c r="E49" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F49" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" шоколадная 1.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" белая БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G49" s="27" t="n">
-        <v>85170</v>
+        <v>8775</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
@@ -2855,16 +2847,16 @@
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F50" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль по ржавчине 3в1 "ПРОСТОКРАШЕНО!" шоколадная 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" бирюзовая БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G50" s="27" t="n">
-        <v>69716</v>
+        <v>63576</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
@@ -2893,16 +2885,16 @@
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные для радиаторов</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>Эмаль "ПРОСТОКРАШЕНО!" алкидная для радиаторов отопления 0.9 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" васильковая БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G51" s="27" t="n">
-        <v>86082</v>
+        <v>63580</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
@@ -2936,11 +2928,11 @@
       </c>
       <c r="F52" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" бежевая БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" вишнёвая БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G52" s="27" t="n">
-        <v>81295</v>
+        <v>63572</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -2974,11 +2966,11 @@
       </c>
       <c r="F53" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" белая БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" голубая БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G53" s="27" t="n">
-        <v>81277</v>
+        <v>81278</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -3012,11 +3004,11 @@
       </c>
       <c r="F54" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" белая БАУЦЕНТР 1.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" голубая БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G54" s="27" t="n">
-        <v>85171</v>
+        <v>85172</v>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
@@ -3050,11 +3042,11 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" белая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" жёлтая БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G55" s="27" t="n">
-        <v>8775</v>
+        <v>81279</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
@@ -3088,15 +3080,15 @@
       </c>
       <c r="F56" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" бирюзовая БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" жёлтая БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G56" s="27" t="n">
-        <v>81290</v>
+        <v>85173</v>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3118,15 @@
       </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" бирюзовая БАУЦЕНТР 1.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" зелёная БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G57" s="27" t="n">
-        <v>85184</v>
+        <v>81280</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3164,15 +3156,15 @@
       </c>
       <c r="F58" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" бирюзовая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" зелёная БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G58" s="27" t="n">
-        <v>63576</v>
+        <v>85174</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3202,15 +3194,15 @@
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" васильковая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" зелёная БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G59" s="27" t="n">
-        <v>63580</v>
+        <v>8832</v>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3240,15 +3232,15 @@
       </c>
       <c r="F60" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" вишнёвая БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" коричневая БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G60" s="27" t="n">
-        <v>81289</v>
+        <v>81296</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3278,15 +3270,15 @@
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" вишнёвая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" коричневая БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G61" s="27" t="n">
-        <v>63572</v>
+        <v>85190</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3316,15 +3308,15 @@
       </c>
       <c r="F62" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" голубая БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" коричневая БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G62" s="27" t="n">
-        <v>81278</v>
+        <v>63600</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -3354,11 +3346,11 @@
       </c>
       <c r="F63" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" голубая БАУЦЕНТР 1.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" красная БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G63" s="27" t="n">
-        <v>85172</v>
+        <v>81281</v>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
@@ -3392,15 +3384,15 @@
       </c>
       <c r="F64" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" голубая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" красная БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G64" s="27" t="n">
-        <v>8799</v>
+        <v>85175</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3422,15 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" жёлтая БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" красная БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G65" s="27" t="n">
-        <v>81279</v>
+        <v>8850</v>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3460,11 @@
       </c>
       <c r="F66" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" жёлтая БАУЦЕНТР 1.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" серая БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G66" s="27" t="n">
-        <v>85173</v>
+        <v>81283</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -3506,15 +3498,15 @@
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" жёлтая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" серая БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G67" s="27" t="n">
-        <v>8815</v>
+        <v>85177</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3544,11 +3536,11 @@
       </c>
       <c r="F68" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" зелёная БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" серая БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G68" s="27" t="n">
-        <v>81280</v>
+        <v>8882</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -3582,11 +3574,11 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" зелёная БАУЦЕНТР 1.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" синяя БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G69" s="27" t="n">
-        <v>85174</v>
+        <v>81284</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
@@ -3620,11 +3612,11 @@
       </c>
       <c r="F70" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" зелёная БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" синяя БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G70" s="27" t="n">
-        <v>8832</v>
+        <v>85178</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -3658,11 +3650,11 @@
       </c>
       <c r="F71" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" коричневая БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" синяя БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G71" s="27" t="n">
-        <v>81296</v>
+        <v>8901</v>
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
@@ -3696,11 +3688,11 @@
       </c>
       <c r="F72" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" коричневая БАУЦЕНТР 1.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" тёмно-зелёная БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G72" s="27" t="n">
-        <v>85190</v>
+        <v>85187</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -3734,15 +3726,15 @@
       </c>
       <c r="F73" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" коричневая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" чёрная БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G73" s="27" t="n">
-        <v>63600</v>
+        <v>81285</v>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3772,11 +3764,11 @@
       </c>
       <c r="F74" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" красная БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" чёрная БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G74" s="27" t="n">
-        <v>81281</v>
+        <v>85179</v>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
@@ -3810,11 +3802,11 @@
       </c>
       <c r="F75" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" красная БАУЦЕНТР 1.8 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" шоколадная БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G75" s="27" t="n">
-        <v>85175</v>
+        <v>81287</v>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
@@ -3848,15 +3840,15 @@
       </c>
       <c r="F76" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" красная БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" шоколадная БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G76" s="27" t="n">
-        <v>8850</v>
+        <v>85181</v>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3876,21 +3868,21 @@
       </c>
       <c r="D77" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E77" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F77" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" оранжевая БАУЦЕНТР 0.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 белая 0.9 кг</t>
         </is>
       </c>
       <c r="G77" s="27" t="n">
-        <v>81288</v>
+        <v>65172</v>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
@@ -3914,25 +3906,25 @@
       </c>
       <c r="D78" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E78" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F78" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" светло-зелёная БАУЦЕНТР 0.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 белая 1.9 кг</t>
         </is>
       </c>
       <c r="G78" s="27" t="n">
-        <v>81292</v>
+        <v>65173</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3952,25 +3944,25 @@
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E79" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F79" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" серая БАУЦЕНТР 0.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 белая 2.7 кг</t>
         </is>
       </c>
       <c r="G79" s="27" t="n">
-        <v>81283</v>
+        <v>65174</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -3990,25 +3982,25 @@
       </c>
       <c r="D80" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E80" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F80" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" серая БАУЦЕНТР 1.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 0.9 кг</t>
         </is>
       </c>
       <c r="G80" s="27" t="n">
-        <v>85177</v>
+        <v>65198</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4028,21 +4020,21 @@
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E81" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F81" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" серая БАУЦЕНТР 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 1.9 кг</t>
         </is>
       </c>
       <c r="G81" s="27" t="n">
-        <v>8882</v>
+        <v>65199</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -4066,25 +4058,25 @@
       </c>
       <c r="D82" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E82" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F82" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" синяя БАУЦЕНТР 0.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 2.7 кг</t>
         </is>
       </c>
       <c r="G82" s="27" t="n">
-        <v>81284</v>
+        <v>65200</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4104,25 +4096,25 @@
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E83" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F83" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" синяя БАУЦЕНТР 1.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 голубая 0.9 кг</t>
         </is>
       </c>
       <c r="G83" s="27" t="n">
-        <v>85178</v>
+        <v>65189</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4142,25 +4134,25 @@
       </c>
       <c r="D84" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E84" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F84" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" синяя БАУЦЕНТР 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 0.9 кг</t>
         </is>
       </c>
       <c r="G84" s="27" t="n">
-        <v>8901</v>
+        <v>65204</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4180,21 +4172,21 @@
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E85" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F85" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" сиреневая БАУЦЕНТР 0.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 1.9 кг</t>
         </is>
       </c>
       <c r="G85" s="27" t="n">
-        <v>81294</v>
+        <v>65205</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
@@ -4218,25 +4210,25 @@
       </c>
       <c r="D86" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E86" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F86" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" тёмно-зелёная БАУЦЕНТР 0.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 2.7 кг</t>
         </is>
       </c>
       <c r="G86" s="27" t="n">
-        <v>81293</v>
+        <v>65206</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4256,25 +4248,25 @@
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E87" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F87" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" тёмно-зелёная БАУЦЕНТР 1.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 0.9 кг</t>
         </is>
       </c>
       <c r="G87" s="27" t="n">
-        <v>85187</v>
+        <v>65192</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4294,25 +4286,25 @@
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E88" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F88" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" тёмно-зелёная БАУЦЕНТР 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 1.9 кг</t>
         </is>
       </c>
       <c r="G88" s="27" t="n">
-        <v>63588</v>
+        <v>65193</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4332,25 +4324,25 @@
       </c>
       <c r="D89" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E89" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F89" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" чёрная БАУЦЕНТР 0.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 2.7 кг</t>
         </is>
       </c>
       <c r="G89" s="27" t="n">
-        <v>81285</v>
+        <v>65194</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4370,25 +4362,25 @@
       </c>
       <c r="D90" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E90" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F90" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" чёрная БАУЦЕНТР 1.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 0.9 кг</t>
         </is>
       </c>
       <c r="G90" s="27" t="n">
-        <v>85179</v>
+        <v>72966</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4408,21 +4400,21 @@
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E91" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F91" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" чёрная БАУЦЕНТР 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 1.9 кг</t>
         </is>
       </c>
       <c r="G91" s="27" t="n">
-        <v>8920</v>
+        <v>72968</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
@@ -4446,25 +4438,25 @@
       </c>
       <c r="D92" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E92" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F92" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" шоколадная БАУЦЕНТР 0.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 2.7 кг</t>
         </is>
       </c>
       <c r="G92" s="27" t="n">
-        <v>81287</v>
+        <v>72971</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4484,21 +4476,21 @@
       </c>
       <c r="D93" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E93" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F93" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" шоколадная БАУЦЕНТР 1.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 0.9 кг</t>
         </is>
       </c>
       <c r="G93" s="27" t="n">
-        <v>85181</v>
+        <v>65176</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
@@ -4522,25 +4514,25 @@
       </c>
       <c r="D94" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E94" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F94" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" шоколадная БАУЦЕНТР 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 1.9 кг</t>
         </is>
       </c>
       <c r="G94" s="27" t="n">
-        <v>50015</v>
+        <v>65177</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4560,25 +4552,25 @@
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E95" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F95" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" ярко-зелёная БАУЦЕНТР 0.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 2.7 кг</t>
         </is>
       </c>
       <c r="G95" s="27" t="n">
-        <v>81286</v>
+        <v>65178</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4598,21 +4590,21 @@
       </c>
       <c r="D96" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E96" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F96" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" ярко-зелёная БАУЦЕНТР 1.8 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 5 кг</t>
         </is>
       </c>
       <c r="G96" s="27" t="n">
-        <v>85180</v>
+        <v>70246</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
@@ -4636,21 +4628,21 @@
       </c>
       <c r="D97" s="27" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E97" s="27" t="inlineStr">
         <is>
-          <t>Эмали Алкидные</t>
+          <t>Грунт-Эмаль</t>
         </is>
       </c>
       <c r="F97" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 "ПРОСТОКРАШЕНО!" ярко-зелёная БАУЦЕНТР 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 0.9 кг</t>
         </is>
       </c>
       <c r="G97" s="27" t="n">
-        <v>8935</v>
+        <v>87388</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -4684,15 +4676,15 @@
       </c>
       <c r="F98" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 белая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 1.9 кг</t>
         </is>
       </c>
       <c r="G98" s="27" t="n">
-        <v>65172</v>
+        <v>87389</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4722,15 +4714,15 @@
       </c>
       <c r="F99" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 белая 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 2.7 кг</t>
         </is>
       </c>
       <c r="G99" s="27" t="n">
-        <v>65173</v>
+        <v>87390</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4760,11 +4752,11 @@
       </c>
       <c r="F100" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 белая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 0.9 кг</t>
         </is>
       </c>
       <c r="G100" s="27" t="n">
-        <v>65174</v>
+        <v>65201</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
@@ -4798,15 +4790,15 @@
       </c>
       <c r="F101" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 1.9 кг</t>
         </is>
       </c>
       <c r="G101" s="27" t="n">
-        <v>65198</v>
+        <v>65202</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4836,15 +4828,15 @@
       </c>
       <c r="F102" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 2.7 кг</t>
         </is>
       </c>
       <c r="G102" s="27" t="n">
-        <v>65199</v>
+        <v>65203</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4874,11 +4866,11 @@
       </c>
       <c r="F103" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 тёмно-зелёная 0.9 кг</t>
         </is>
       </c>
       <c r="G103" s="27" t="n">
-        <v>65200</v>
+        <v>72960</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
@@ -4912,15 +4904,15 @@
       </c>
       <c r="F104" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 голубая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 0.9 кг</t>
         </is>
       </c>
       <c r="G104" s="27" t="n">
-        <v>65189</v>
+        <v>65186</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4950,15 +4942,15 @@
       </c>
       <c r="F105" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 1.9 кг</t>
         </is>
       </c>
       <c r="G105" s="27" t="n">
-        <v>65204</v>
+        <v>65187</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4988,11 +4980,11 @@
       </c>
       <c r="F106" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 2.7 кг</t>
         </is>
       </c>
       <c r="G106" s="27" t="n">
-        <v>65205</v>
+        <v>65188</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -5026,15 +5018,15 @@
       </c>
       <c r="F107" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 5 кг</t>
         </is>
       </c>
       <c r="G107" s="27" t="n">
-        <v>65206</v>
+        <v>70253</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5064,15 +5056,15 @@
       </c>
       <c r="F108" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 0.9 кг</t>
         </is>
       </c>
       <c r="G108" s="27" t="n">
-        <v>65192</v>
+        <v>65195</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -5102,11 +5094,11 @@
       </c>
       <c r="F109" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 1.9 кг</t>
         </is>
       </c>
       <c r="G109" s="27" t="n">
-        <v>65193</v>
+        <v>65196</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
@@ -5140,15 +5132,15 @@
       </c>
       <c r="F110" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 2.7 кг</t>
         </is>
       </c>
       <c r="G110" s="27" t="n">
-        <v>65194</v>
+        <v>65197</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5178,15 +5170,15 @@
       </c>
       <c r="F111" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 0.9 кг</t>
+          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая серая 0.9 кг</t>
         </is>
       </c>
       <c r="G111" s="27" t="n">
-        <v>72966</v>
+        <v>82704</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5216,11 +5208,11 @@
       </c>
       <c r="F112" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 1.9 кг</t>
+          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая черная 0.9 кг</t>
         </is>
       </c>
       <c r="G112" s="27" t="n">
-        <v>72968</v>
+        <v>82708</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -5254,15 +5246,15 @@
       </c>
       <c r="F113" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 2.7 кг</t>
+          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая черная 2.7 кг</t>
         </is>
       </c>
       <c r="G113" s="27" t="n">
-        <v>72971</v>
+        <v>82709</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5287,20 +5279,20 @@
       </c>
       <c r="E114" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F114" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 0.9 кг</t>
+          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G114" s="27" t="n">
-        <v>65176</v>
+        <v>9039</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5325,20 +5317,20 @@
       </c>
       <c r="E115" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F115" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 1.9 кг</t>
+          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G115" s="27" t="n">
-        <v>65177</v>
+        <v>9040</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5363,16 +5355,16 @@
       </c>
       <c r="E116" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F116" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 2.7 кг</t>
+          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G116" s="27" t="n">
-        <v>65178</v>
+        <v>9041</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
@@ -5401,20 +5393,20 @@
       </c>
       <c r="E117" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F117" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 5 кг</t>
+          <t>Эмаль ПФ-115 вишнёвая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G117" s="27" t="n">
-        <v>70246</v>
+        <v>9064</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5439,20 +5431,20 @@
       </c>
       <c r="E118" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F118" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 0.9 кг</t>
+          <t>Эмаль ПФ-115 голубая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G118" s="27" t="n">
-        <v>87388</v>
+        <v>9090</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5477,20 +5469,20 @@
       </c>
       <c r="E119" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F119" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 1.9 кг</t>
+          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G119" s="27" t="n">
-        <v>87389</v>
+        <v>9212</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5515,20 +5507,20 @@
       </c>
       <c r="E120" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F120" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 2.7 кг</t>
+          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G120" s="27" t="n">
-        <v>87390</v>
+        <v>9213</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5553,20 +5545,20 @@
       </c>
       <c r="E121" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F121" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 0.9 кг</t>
+          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G121" s="27" t="n">
-        <v>65201</v>
+        <v>9214</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5591,20 +5583,20 @@
       </c>
       <c r="E122" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F122" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 1.9 кг</t>
+          <t>Эмаль ПФ-115 коричневая РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G122" s="27" t="n">
-        <v>65202</v>
+        <v>9232</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5629,16 +5621,16 @@
       </c>
       <c r="E123" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F123" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 2.7 кг</t>
+          <t>Эмаль ПФ-115 коричневая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G123" s="27" t="n">
-        <v>65203</v>
+        <v>9234</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
@@ -5667,20 +5659,20 @@
       </c>
       <c r="E124" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F124" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 тёмно-зелёная 0.9 кг</t>
+          <t>Эмаль ПФ-115 красная РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G124" s="27" t="n">
-        <v>72960</v>
+        <v>9258</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5705,20 +5697,20 @@
       </c>
       <c r="E125" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F125" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 0.9 кг</t>
+          <t>Эмаль ПФ-115 красная РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G125" s="27" t="n">
-        <v>65186</v>
+        <v>9260</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5743,20 +5735,20 @@
       </c>
       <c r="E126" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F126" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 1.9 кг</t>
+          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G126" s="27" t="n">
-        <v>65187</v>
+        <v>9749</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5781,20 +5773,20 @@
       </c>
       <c r="E127" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F127" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 2.7 кг</t>
+          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G127" s="27" t="n">
-        <v>65188</v>
+        <v>9750</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -5819,16 +5811,16 @@
       </c>
       <c r="E128" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F128" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 5 кг</t>
+          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G128" s="27" t="n">
-        <v>70253</v>
+        <v>9751</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5857,20 +5849,20 @@
       </c>
       <c r="E129" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F129" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 0.9 кг</t>
+          <t>Эмаль ПФ-115 синяя РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G129" s="27" t="n">
-        <v>65195</v>
+        <v>9781</v>
       </c>
       <c r="H129" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5895,20 +5887,20 @@
       </c>
       <c r="E130" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F130" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 1.9 кг</t>
+          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G130" s="27" t="n">
-        <v>65196</v>
+        <v>10093</v>
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5933,16 +5925,16 @@
       </c>
       <c r="E131" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F131" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 2.7 кг</t>
+          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G131" s="27" t="n">
-        <v>65197</v>
+        <v>10094</v>
       </c>
       <c r="H131" s="14" t="inlineStr">
         <is>
@@ -5971,20 +5963,20 @@
       </c>
       <c r="E132" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F132" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая серая 0.9 кг</t>
+          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G132" s="27" t="n">
-        <v>82704</v>
+        <v>10095</v>
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -6009,20 +6001,20 @@
       </c>
       <c r="E133" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F133" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая черная 0.9 кг</t>
+          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G133" s="27" t="n">
-        <v>82708</v>
+        <v>10102</v>
       </c>
       <c r="H133" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -6047,16 +6039,16 @@
       </c>
       <c r="E134" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F134" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая черная 2.7 кг</t>
+          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G134" s="27" t="n">
-        <v>82709</v>
+        <v>10103</v>
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
@@ -6090,11 +6082,11 @@
       </c>
       <c r="F135" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 0.9 кг</t>
+          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G135" s="27" t="n">
-        <v>9039</v>
+        <v>10104</v>
       </c>
       <c r="H135" s="14" t="inlineStr">
         <is>
@@ -6128,11 +6120,11 @@
       </c>
       <c r="F136" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 1.9 кг</t>
+          <t>Эмаль ПФ-115 ярко-жёлтая РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G136" s="27" t="n">
-        <v>9040</v>
+        <v>10179</v>
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
@@ -6166,15 +6158,15 @@
       </c>
       <c r="F137" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль ПФ-115 ярко-жёлтая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G137" s="27" t="n">
-        <v>9041</v>
+        <v>10181</v>
       </c>
       <c r="H137" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -6204,11 +6196,11 @@
       </c>
       <c r="F138" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 вишнёвая РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль с молотковым эффектом РАСЦВЕТ коричневая 0.8 кг</t>
         </is>
       </c>
       <c r="G138" s="27" t="n">
-        <v>9064</v>
+        <v>77633</v>
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
@@ -6242,11 +6234,11 @@
       </c>
       <c r="F139" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 голубая РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль с молотковым эффектом РАСЦВЕТ чёрная 0.8 кг</t>
         </is>
       </c>
       <c r="G139" s="27" t="n">
-        <v>9090</v>
+        <v>77618</v>
       </c>
       <c r="H139" s="14" t="inlineStr">
         <is>
@@ -6280,15 +6272,15 @@
       </c>
       <c r="F140" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 0.9 кг</t>
+          <t>Эмаль универсальная ПФ-115 Расцвет белая матовая 0.9 кг</t>
         </is>
       </c>
       <c r="G140" s="27" t="n">
-        <v>9212</v>
+        <v>10816</v>
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -6318,851 +6310,851 @@
       </c>
       <c r="F141" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 1.9 кг</t>
+          <t>Эмаль универсальная ПФ-115 Расцвет белая матовая 2.7 кг</t>
         </is>
       </c>
       <c r="G141" s="27" t="n">
-        <v>9213</v>
+        <v>10818</v>
       </c>
       <c r="H141" s="14" t="inlineStr">
         <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="17" t="n">
+        <v>139</v>
+      </c>
+      <c r="B142" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C142" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D142" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E142" s="30" t="inlineStr">
+        <is>
+          <t>Грунтовки</t>
+        </is>
+      </c>
+      <c r="F142" s="30" t="inlineStr">
+        <is>
+          <t>Грунтовка глубокого проникновения с антисептиком «NEWTONE» водно-дисперсионная полиакриловая для наружных и внутренних работ</t>
+        </is>
+      </c>
+      <c r="G142" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="B143" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C143" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D143" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E143" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F143" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE INTERIO» суперстойкая интерьерная водно-дисперсионная латексная матовая (База C)</t>
+        </is>
+      </c>
+      <c r="G143" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="B144" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C144" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D144" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E144" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F144" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE INTERIO» суперстойкая интерьерная водно-дисперсионная латексная матовая (База А)</t>
+        </is>
+      </c>
+      <c r="G144" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="17" t="n">
+        <v>142</v>
+      </c>
+      <c r="B145" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C145" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D145" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E145" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F145" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 20» моющаяся интерьерная водно-дисперсионная латексная полуматовая (База A)</t>
+        </is>
+      </c>
+      <c r="G145" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="n">
+        <v>143</v>
+      </c>
+      <c r="B146" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C146" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D146" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E146" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F146" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 20» моющаяся интерьерная водно-дисперсионная латексная полуматовая (База C)</t>
+        </is>
+      </c>
+      <c r="G146" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="17" t="n">
+        <v>144</v>
+      </c>
+      <c r="B147" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C147" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D147" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E147" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F147" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 3» моющаяся интерьерная водно-дисперсионная латексная глубокоматовая (База C)</t>
+        </is>
+      </c>
+      <c r="G147" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="17" t="n">
+        <v>145</v>
+      </c>
+      <c r="B148" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C148" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D148" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E148" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F148" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 3» моющаяся интерьерная водно-дисперсионная латексная глубокоматовая (База А)</t>
+        </is>
+      </c>
+      <c r="G148" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="B149" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C149" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D149" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E149" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F149" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 7» моющаяся интерьерная водно-дисперсионная латексная матовая (База C)</t>
+        </is>
+      </c>
+      <c r="G149" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="17" t="n">
+        <v>147</v>
+      </c>
+      <c r="B150" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C150" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D150" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E150" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F150" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 7» моющаяся интерьерная водно-дисперсионная латексная матовая (База А)</t>
+        </is>
+      </c>
+      <c r="G150" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="17" t="n">
+        <v>148</v>
+      </c>
+      <c r="B151" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C151" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D151" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E151" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F151" s="30" t="inlineStr">
+        <is>
+          <t>Краска ВД «NEWTONE SKY» для потолков ультрабелая водно-дисперсионная латексная</t>
+        </is>
+      </c>
+      <c r="G151" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="17" t="n">
+        <v>149</v>
+      </c>
+      <c r="B152" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C152" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D152" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E152" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F152" s="30" t="inlineStr">
+        <is>
+          <t>Краска для интерьеров моющаяся глубокоматовая «NEWTONE» водно-дисперсионная полиакриловая для внутренних работ черная RAL 9005</t>
+        </is>
+      </c>
+      <c r="G152" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="B153" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C153" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D153" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E153" s="30" t="inlineStr">
+        <is>
+          <t>Шпатлёвки</t>
+        </is>
+      </c>
+      <c r="F153" s="30" t="inlineStr">
+        <is>
+          <t>Шпатлевка супер финишная «NEWTONE» водно-дисперсионная полиакриловая для внутренних работ</t>
+        </is>
+      </c>
+      <c r="G153" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="17" t="n">
+        <v>151</v>
+      </c>
+      <c r="B154" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C154" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D154" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E154" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F154" s="30" t="inlineStr">
+        <is>
+          <t>Краска ВД Ореол белоснежная для потолков 3 кг</t>
+        </is>
+      </c>
+      <c r="G154" s="30" t="n">
+        <v>5372</v>
+      </c>
+      <c r="H154" s="17" t="inlineStr">
+        <is>
           <t>В</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="14" t="n">
-        <v>139</v>
-      </c>
-      <c r="B142" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C142" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D142" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E142" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F142" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G142" s="27" t="n">
-        <v>9214</v>
-      </c>
-      <c r="H142" s="14" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="17" t="n">
+        <v>152</v>
+      </c>
+      <c r="B155" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C155" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D155" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E155" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F155" s="30" t="inlineStr">
+        <is>
+          <t>Краска ВД Ореол белоснежная для стен и потолков 13 кг</t>
+        </is>
+      </c>
+      <c r="G155" s="30" t="n">
+        <v>5385</v>
+      </c>
+      <c r="H155" s="17" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="17" t="n">
+        <v>153</v>
+      </c>
+      <c r="B156" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C156" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D156" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E156" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F156" s="30" t="inlineStr">
+        <is>
+          <t>Краска ВД Ореол белоснежная для стен и потолков 3 кг</t>
+        </is>
+      </c>
+      <c r="G156" s="30" t="n">
+        <v>5390</v>
+      </c>
+      <c r="H156" s="17" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="14" t="n">
-        <v>140</v>
-      </c>
-      <c r="B143" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C143" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D143" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E143" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F143" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 коричневая РАСЦВЕТ ГОСТ 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G143" s="27" t="n">
-        <v>9232</v>
-      </c>
-      <c r="H143" s="14" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="17" t="n">
+        <v>154</v>
+      </c>
+      <c r="B157" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C157" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D157" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E157" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F157" s="30" t="inlineStr">
+        <is>
+          <t>Краска ВД Ореол белоснежная для стен и потолков 6.5 кг</t>
+        </is>
+      </c>
+      <c r="G157" s="30" t="n">
+        <v>5396</v>
+      </c>
+      <c r="H157" s="17" t="inlineStr">
         <is>
           <t>С</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="14" t="n">
-        <v>141</v>
-      </c>
-      <c r="B144" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C144" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D144" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E144" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F144" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 коричневая РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G144" s="27" t="n">
-        <v>9234</v>
-      </c>
-      <c r="H144" s="14" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="B158" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C158" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D158" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E158" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F158" s="30" t="inlineStr">
+        <is>
+          <t>Краска ВД Ореол для стен и потолков моющаяся 3 кг</t>
+        </is>
+      </c>
+      <c r="G158" s="30" t="n">
+        <v>5468</v>
+      </c>
+      <c r="H158" s="17" t="inlineStr">
         <is>
           <t>С</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="14" t="n">
-        <v>142</v>
-      </c>
-      <c r="B145" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C145" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D145" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E145" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F145" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 красная РАСЦВЕТ ГОСТ 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G145" s="27" t="n">
-        <v>9258</v>
-      </c>
-      <c r="H145" s="14" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="17" t="n">
+        <v>156</v>
+      </c>
+      <c r="B159" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C159" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D159" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E159" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F159" s="30" t="inlineStr">
+        <is>
+          <t>Краска ВД Ореол для стен и потолков моющаяся 6.5 кг</t>
+        </is>
+      </c>
+      <c r="G159" s="30" t="n">
+        <v>5470</v>
+      </c>
+      <c r="H159" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="17" t="n">
+        <v>157</v>
+      </c>
+      <c r="B160" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C160" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D160" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E160" s="30" t="inlineStr">
+        <is>
+          <t>Шпатлёвки</t>
+        </is>
+      </c>
+      <c r="F160" s="30" t="inlineStr">
+        <is>
+          <t>Шпатлевка Ореол фасадная влагостойкая ВД акриловая 1.5 кг</t>
+        </is>
+      </c>
+      <c r="G160" s="30" t="n">
+        <v>66128</v>
+      </c>
+      <c r="H160" s="17" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="14" t="n">
-        <v>143</v>
-      </c>
-      <c r="B146" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C146" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D146" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E146" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F146" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 красная РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G146" s="27" t="n">
-        <v>9260</v>
-      </c>
-      <c r="H146" s="14" t="inlineStr">
-        <is>
-          <t>С</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="14" t="n">
-        <v>144</v>
-      </c>
-      <c r="B147" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C147" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D147" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E147" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F147" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G147" s="27" t="n">
-        <v>9749</v>
-      </c>
-      <c r="H147" s="14" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="17" t="n">
+        <v>158</v>
+      </c>
+      <c r="B161" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C161" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D161" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E161" s="30" t="inlineStr">
+        <is>
+          <t>Эмали ВДАК</t>
+        </is>
+      </c>
+      <c r="F161" s="30" t="inlineStr">
+        <is>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая белая (пластиковая тара) 0.9 кг</t>
+        </is>
+      </c>
+      <c r="G161" s="30" t="n">
+        <v>70644</v>
+      </c>
+      <c r="H161" s="17" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="17" t="n">
+        <v>159</v>
+      </c>
+      <c r="B162" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C162" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D162" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E162" s="30" t="inlineStr">
+        <is>
+          <t>Эмали ВДАК</t>
+        </is>
+      </c>
+      <c r="F162" s="30" t="inlineStr">
+        <is>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая белая 2.5 кг</t>
+        </is>
+      </c>
+      <c r="G162" s="30" t="n">
+        <v>85884</v>
+      </c>
+      <c r="H162" s="17" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="B163" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C163" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D163" s="30" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E163" s="30" t="inlineStr">
+        <is>
+          <t>Эмали ВДАК</t>
+        </is>
+      </c>
+      <c r="F163" s="30" t="inlineStr">
+        <is>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая серая 0.9 кг</t>
+        </is>
+      </c>
+      <c r="G163" s="30" t="n">
+        <v>65254</v>
+      </c>
+      <c r="H163" s="17" t="inlineStr">
         <is>
           <t>В</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="14" t="n">
-        <v>145</v>
-      </c>
-      <c r="B148" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C148" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D148" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E148" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F148" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 1.9 кг</t>
-        </is>
-      </c>
-      <c r="G148" s="27" t="n">
-        <v>9750</v>
-      </c>
-      <c r="H148" s="14" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="14" t="n">
-        <v>146</v>
-      </c>
-      <c r="B149" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C149" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D149" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E149" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F149" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G149" s="27" t="n">
-        <v>9751</v>
-      </c>
-      <c r="H149" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="14" t="n">
-        <v>147</v>
-      </c>
-      <c r="B150" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C150" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D150" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E150" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F150" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 синяя РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G150" s="27" t="n">
-        <v>9781</v>
-      </c>
-      <c r="H150" s="14" t="inlineStr">
-        <is>
-          <t>С</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="14" t="n">
-        <v>148</v>
-      </c>
-      <c r="B151" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C151" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D151" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E151" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F151" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G151" s="27" t="n">
-        <v>10093</v>
-      </c>
-      <c r="H151" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="14" t="n">
-        <v>149</v>
-      </c>
-      <c r="B152" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C152" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D152" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E152" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F152" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 1.9 кг</t>
-        </is>
-      </c>
-      <c r="G152" s="27" t="n">
-        <v>10094</v>
-      </c>
-      <c r="H152" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="14" t="n">
-        <v>150</v>
-      </c>
-      <c r="B153" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C153" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D153" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E153" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F153" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G153" s="27" t="n">
-        <v>10095</v>
-      </c>
-      <c r="H153" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="14" t="n">
-        <v>151</v>
-      </c>
-      <c r="B154" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C154" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D154" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E154" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F154" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G154" s="27" t="n">
-        <v>10102</v>
-      </c>
-      <c r="H154" s="14" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="14" t="n">
-        <v>152</v>
-      </c>
-      <c r="B155" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C155" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D155" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E155" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F155" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 1.9 кг</t>
-        </is>
-      </c>
-      <c r="G155" s="27" t="n">
-        <v>10103</v>
-      </c>
-      <c r="H155" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="14" t="n">
-        <v>153</v>
-      </c>
-      <c r="B156" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C156" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D156" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E156" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F156" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G156" s="27" t="n">
-        <v>10104</v>
-      </c>
-      <c r="H156" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="14" t="n">
-        <v>154</v>
-      </c>
-      <c r="B157" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C157" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D157" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E157" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F157" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 ярко-жёлтая РАСЦВЕТ ГОСТ 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G157" s="27" t="n">
-        <v>10179</v>
-      </c>
-      <c r="H157" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="14" t="n">
-        <v>155</v>
-      </c>
-      <c r="B158" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C158" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D158" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E158" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F158" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 ярко-жёлтая РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G158" s="27" t="n">
-        <v>10181</v>
-      </c>
-      <c r="H158" s="14" t="inlineStr">
-        <is>
-          <t>С</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="14" t="n">
-        <v>156</v>
-      </c>
-      <c r="B159" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C159" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D159" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E159" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F159" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль с молотковым эффектом РАСЦВЕТ коричневая 0.8 кг</t>
-        </is>
-      </c>
-      <c r="G159" s="27" t="n">
-        <v>77633</v>
-      </c>
-      <c r="H159" s="14" t="inlineStr">
-        <is>
-          <t>С</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="14" t="n">
-        <v>157</v>
-      </c>
-      <c r="B160" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C160" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D160" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E160" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F160" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль с молотковым эффектом РАСЦВЕТ чёрная 0.8 кг</t>
-        </is>
-      </c>
-      <c r="G160" s="27" t="n">
-        <v>77618</v>
-      </c>
-      <c r="H160" s="14" t="inlineStr">
-        <is>
-          <t>С</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="14" t="n">
-        <v>158</v>
-      </c>
-      <c r="B161" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C161" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D161" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E161" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F161" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль универсальная ПФ-115 Расцвет белая матовая 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G161" s="27" t="n">
-        <v>10816</v>
-      </c>
-      <c r="H161" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="14" t="n">
-        <v>159</v>
-      </c>
-      <c r="B162" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C162" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D162" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E162" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F162" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль универсальная ПФ-115 Расцвет белая матовая 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G162" s="27" t="n">
-        <v>10818</v>
-      </c>
-      <c r="H162" s="14" t="inlineStr">
-        <is>
-          <t>С</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="14" t="n">
-        <v>160</v>
-      </c>
-      <c r="B163" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C163" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D163" s="27" t="inlineStr">
-        <is>
-          <t>СТРОЙКОМПЛЕКТ</t>
-        </is>
-      </c>
-      <c r="E163" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F163" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 СТРОЙКОМПЛЕКТ чёрная 10 кг</t>
-        </is>
-      </c>
-      <c r="G163" s="27" t="n">
-        <v>72676</v>
-      </c>
-      <c r="H163" s="14" t="inlineStr">
-        <is>
-          <t>А</t>
         </is>
       </c>
     </row>
@@ -7187,20 +7179,20 @@
       </c>
       <c r="E164" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F164" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол белоснежная для потолков 3 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая слоновая кость 0.9 кг</t>
         </is>
       </c>
       <c r="G164" s="30" t="n">
-        <v>5372</v>
+        <v>78181</v>
       </c>
       <c r="H164" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -7225,20 +7217,20 @@
       </c>
       <c r="E165" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F165" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол белоснежная для стен и потолков 13 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая черная 0.9 кг</t>
         </is>
       </c>
       <c r="G165" s="30" t="n">
-        <v>5385</v>
+        <v>65252</v>
       </c>
       <c r="H165" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -7263,20 +7255,20 @@
       </c>
       <c r="E166" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F166" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол белоснежная для стен и потолков 3 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" матовая белая (пластиковая тара) 0.9 кг</t>
         </is>
       </c>
       <c r="G166" s="30" t="n">
-        <v>5390</v>
+        <v>70661</v>
       </c>
       <c r="H166" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7301,20 +7293,20 @@
       </c>
       <c r="E167" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F167" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол белоснежная для стен и потолков 6.5 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" матовая белая (пластиковая тара) 2.5 кг</t>
         </is>
       </c>
       <c r="G167" s="30" t="n">
-        <v>5396</v>
+        <v>70662</v>
       </c>
       <c r="H167" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7339,16 +7331,16 @@
       </c>
       <c r="E168" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F168" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол для стен и потолков моющаяся 3 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" матовая серая 0.9 кг</t>
         </is>
       </c>
       <c r="G168" s="30" t="n">
-        <v>5468</v>
+        <v>71787</v>
       </c>
       <c r="H168" s="17" t="inlineStr">
         <is>
@@ -7377,16 +7369,16 @@
       </c>
       <c r="E169" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F169" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол для стен и потолков моющаяся 6.5 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" матовая чёрная 0.9 кг</t>
         </is>
       </c>
       <c r="G169" s="30" t="n">
-        <v>5470</v>
+        <v>71790</v>
       </c>
       <c r="H169" s="17" t="inlineStr">
         <is>
@@ -7410,25 +7402,25 @@
       </c>
       <c r="D170" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E170" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F170" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка Ореол фасадная влагостойкая ВД акриловая 1.5 кг</t>
+          <t>Грунт-концентрат ВД-ВА Ореол Дисконт 1 кг</t>
         </is>
       </c>
       <c r="G170" s="30" t="n">
-        <v>66128</v>
+        <v>4209</v>
       </c>
       <c r="H170" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7448,25 +7440,25 @@
       </c>
       <c r="D171" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E171" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F171" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая белая (пластиковая тара) 0.9 кг</t>
+          <t>Грунт-концентрат ВД-ВА Ореол Дисконт 3 кг</t>
         </is>
       </c>
       <c r="G171" s="30" t="n">
-        <v>70644</v>
+        <v>67654</v>
       </c>
       <c r="H171" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -7486,21 +7478,21 @@
       </c>
       <c r="D172" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E172" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F172" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая белая 2.5 кг</t>
+          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 1 кг</t>
         </is>
       </c>
       <c r="G172" s="30" t="n">
-        <v>85884</v>
+        <v>65722</v>
       </c>
       <c r="H172" s="17" t="inlineStr">
         <is>
@@ -7524,25 +7516,25 @@
       </c>
       <c r="D173" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E173" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F173" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая серая 0.9 кг</t>
+          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 10 кг</t>
         </is>
       </c>
       <c r="G173" s="30" t="n">
-        <v>65254</v>
+        <v>65724</v>
       </c>
       <c r="H173" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7562,25 +7554,25 @@
       </c>
       <c r="D174" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E174" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F174" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая слоновая кость 0.9 кг</t>
+          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 5 кг</t>
         </is>
       </c>
       <c r="G174" s="30" t="n">
-        <v>78181</v>
+        <v>65723</v>
       </c>
       <c r="H174" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7600,21 +7592,21 @@
       </c>
       <c r="D175" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E175" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F175" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая черная 0.9 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 1 кг</t>
         </is>
       </c>
       <c r="G175" s="30" t="n">
-        <v>65252</v>
+        <v>4484</v>
       </c>
       <c r="H175" s="17" t="inlineStr">
         <is>
@@ -7638,21 +7630,21 @@
       </c>
       <c r="D176" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E176" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F176" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" матовая белая (пластиковая тара) 0.9 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 10 кг</t>
         </is>
       </c>
       <c r="G176" s="30" t="n">
-        <v>70661</v>
+        <v>4485</v>
       </c>
       <c r="H176" s="17" t="inlineStr">
         <is>
@@ -7676,21 +7668,21 @@
       </c>
       <c r="D177" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E177" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F177" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" матовая белая (пластиковая тара) 2.5 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 5 кг</t>
         </is>
       </c>
       <c r="G177" s="30" t="n">
-        <v>70662</v>
+        <v>4487</v>
       </c>
       <c r="H177" s="17" t="inlineStr">
         <is>
@@ -7714,25 +7706,25 @@
       </c>
       <c r="D178" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E178" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F178" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" матовая серая 0.9 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 1 кг</t>
         </is>
       </c>
       <c r="G178" s="30" t="n">
-        <v>71787</v>
+        <v>50649</v>
       </c>
       <c r="H178" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -7752,25 +7744,25 @@
       </c>
       <c r="D179" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E179" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F179" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" матовая чёрная 0.9 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 10 кг</t>
         </is>
       </c>
       <c r="G179" s="30" t="n">
-        <v>71790</v>
+        <v>50651</v>
       </c>
       <c r="H179" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -7800,11 +7792,11 @@
       </c>
       <c r="F180" s="30" t="inlineStr">
         <is>
-          <t>Грунт-концентрат ВД-ВА Ореол Дисконт 1 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 5 кг</t>
         </is>
       </c>
       <c r="G180" s="30" t="n">
-        <v>4209</v>
+        <v>50650</v>
       </c>
       <c r="H180" s="17" t="inlineStr">
         <is>
@@ -7833,20 +7825,20 @@
       </c>
       <c r="E181" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F181" s="30" t="inlineStr">
         <is>
-          <t>Грунт-концентрат ВД-ВА Ореол Дисконт 3 кг</t>
+          <t>Краска ВД Ореол Дисконт для потолков супербелая 1.5 кг</t>
         </is>
       </c>
       <c r="G181" s="30" t="n">
-        <v>67654</v>
+        <v>5402</v>
       </c>
       <c r="H181" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7871,16 +7863,16 @@
       </c>
       <c r="E182" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F182" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 1 кг</t>
+          <t>Краска ВД Ореол Дисконт для потолков супербелая 13 кг</t>
         </is>
       </c>
       <c r="G182" s="30" t="n">
-        <v>65722</v>
+        <v>5404</v>
       </c>
       <c r="H182" s="17" t="inlineStr">
         <is>
@@ -7909,16 +7901,16 @@
       </c>
       <c r="E183" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F183" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 10 кг</t>
+          <t>Краска ВД Ореол Дисконт для потолков супербелая 3 кг</t>
         </is>
       </c>
       <c r="G183" s="30" t="n">
-        <v>65724</v>
+        <v>5409</v>
       </c>
       <c r="H183" s="17" t="inlineStr">
         <is>
@@ -7947,16 +7939,16 @@
       </c>
       <c r="E184" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F184" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 5 кг</t>
+          <t>Краска ВД Ореол Дисконт для потолков супербелая 6.5 кг</t>
         </is>
       </c>
       <c r="G184" s="30" t="n">
-        <v>65723</v>
+        <v>5412</v>
       </c>
       <c r="H184" s="17" t="inlineStr">
         <is>
@@ -7985,20 +7977,20 @@
       </c>
       <c r="E185" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F185" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 1 кг</t>
+          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 1.5 кг</t>
         </is>
       </c>
       <c r="G185" s="30" t="n">
-        <v>4484</v>
+        <v>5415</v>
       </c>
       <c r="H185" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8023,16 +8015,16 @@
       </c>
       <c r="E186" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F186" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 10 кг</t>
+          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 13 кг</t>
         </is>
       </c>
       <c r="G186" s="30" t="n">
-        <v>4485</v>
+        <v>5417</v>
       </c>
       <c r="H186" s="17" t="inlineStr">
         <is>
@@ -8061,16 +8053,16 @@
       </c>
       <c r="E187" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F187" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 5 кг</t>
+          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 3 кг</t>
         </is>
       </c>
       <c r="G187" s="30" t="n">
-        <v>4487</v>
+        <v>5420</v>
       </c>
       <c r="H187" s="17" t="inlineStr">
         <is>
@@ -8099,20 +8091,20 @@
       </c>
       <c r="E188" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F188" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 1 кг</t>
+          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 6.5 кг</t>
         </is>
       </c>
       <c r="G188" s="30" t="n">
-        <v>50649</v>
+        <v>5422</v>
       </c>
       <c r="H188" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8137,20 +8129,20 @@
       </c>
       <c r="E189" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F189" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 10 кг</t>
+          <t>Краска ВД Ореол Дисконт интерьерная 1.5 кг</t>
         </is>
       </c>
       <c r="G189" s="30" t="n">
-        <v>50651</v>
+        <v>5424</v>
       </c>
       <c r="H189" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8175,16 +8167,16 @@
       </c>
       <c r="E190" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F190" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 5 кг</t>
+          <t>Краска ВД Ореол Дисконт интерьерная 13 кг</t>
         </is>
       </c>
       <c r="G190" s="30" t="n">
-        <v>50650</v>
+        <v>5426</v>
       </c>
       <c r="H190" s="17" t="inlineStr">
         <is>
@@ -8218,11 +8210,11 @@
       </c>
       <c r="F191" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для потолков супербелая 1.5 кг</t>
+          <t>Краска ВД Ореол Дисконт интерьерная 3 кг</t>
         </is>
       </c>
       <c r="G191" s="30" t="n">
-        <v>5402</v>
+        <v>5429</v>
       </c>
       <c r="H191" s="17" t="inlineStr">
         <is>
@@ -8256,11 +8248,11 @@
       </c>
       <c r="F192" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для потолков супербелая 13 кг</t>
+          <t>Краска ВД Ореол Дисконт интерьерная 6.5 кг</t>
         </is>
       </c>
       <c r="G192" s="30" t="n">
-        <v>5404</v>
+        <v>5431</v>
       </c>
       <c r="H192" s="17" t="inlineStr">
         <is>
@@ -8294,11 +8286,11 @@
       </c>
       <c r="F193" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для потолков супербелая 3 кг</t>
+          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 1.5 кг</t>
         </is>
       </c>
       <c r="G193" s="30" t="n">
-        <v>5409</v>
+        <v>5433</v>
       </c>
       <c r="H193" s="17" t="inlineStr">
         <is>
@@ -8332,11 +8324,11 @@
       </c>
       <c r="F194" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для потолков супербелая 6.5 кг</t>
+          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 13 кг</t>
         </is>
       </c>
       <c r="G194" s="30" t="n">
-        <v>5412</v>
+        <v>5435</v>
       </c>
       <c r="H194" s="17" t="inlineStr">
         <is>
@@ -8370,11 +8362,11 @@
       </c>
       <c r="F195" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 1.5 кг</t>
+          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 3 кг</t>
         </is>
       </c>
       <c r="G195" s="30" t="n">
-        <v>5415</v>
+        <v>5438</v>
       </c>
       <c r="H195" s="17" t="inlineStr">
         <is>
@@ -8408,11 +8400,11 @@
       </c>
       <c r="F196" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 13 кг</t>
+          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 6.5 кг</t>
         </is>
       </c>
       <c r="G196" s="30" t="n">
-        <v>5417</v>
+        <v>5440</v>
       </c>
       <c r="H196" s="17" t="inlineStr">
         <is>
@@ -8429,14 +8421,14 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C197" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C197" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D197" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E197" s="30" t="inlineStr">
@@ -8446,15 +8438,15 @@
       </c>
       <c r="F197" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 3 кг</t>
+          <t>Краска интерьерная моющаяся AvantGarde (база А) матовая белая</t>
         </is>
       </c>
       <c r="G197" s="30" t="n">
-        <v>5420</v>
+        <v>0</v>
       </c>
       <c r="H197" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8467,14 +8459,14 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C198" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C198" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D198" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E198" s="30" t="inlineStr">
@@ -8484,15 +8476,15 @@
       </c>
       <c r="F198" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 6.5 кг</t>
+          <t>Краска интерьерная моющаяся AvantGarde (база С) матовая</t>
         </is>
       </c>
       <c r="G198" s="30" t="n">
-        <v>5422</v>
+        <v>0</v>
       </c>
       <c r="H198" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8505,32 +8497,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C199" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C199" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D199" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E199" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F199" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт интерьерная 1.5 кг</t>
+          <t>Грунт-концентрат АКВАСТОП ОРЕОЛ 1 кг</t>
         </is>
       </c>
       <c r="G199" s="30" t="n">
-        <v>5424</v>
+        <v>66403</v>
       </c>
       <c r="H199" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8543,32 +8535,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C200" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C200" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D200" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E200" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F200" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт интерьерная 13 кг</t>
+          <t>Грунтовка бетон-контакт ОРЕОЛ 12 кг</t>
         </is>
       </c>
       <c r="G200" s="30" t="n">
-        <v>5426</v>
+        <v>66140</v>
       </c>
       <c r="H200" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8581,32 +8573,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C201" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C201" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D201" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E201" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F201" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт интерьерная 3 кг</t>
+          <t>Грунтовка бетон-контакт ОРЕОЛ 3 кг</t>
         </is>
       </c>
       <c r="G201" s="30" t="n">
-        <v>5429</v>
+        <v>66138</v>
       </c>
       <c r="H201" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -8619,32 +8611,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C202" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C202" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D202" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E202" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F202" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт интерьерная 6.5 кг</t>
+          <t>Грунтовка бетон-контакт ОРЕОЛ 6 кг</t>
         </is>
       </c>
       <c r="G202" s="30" t="n">
-        <v>5431</v>
+        <v>66139</v>
       </c>
       <c r="H202" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -8657,32 +8649,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C203" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C203" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D203" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E203" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F203" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 1.5 кг</t>
+          <t>Шпатлевка для влажных помещений ОРЕОЛ  1.5 кг</t>
         </is>
       </c>
       <c r="G203" s="30" t="n">
-        <v>5433</v>
+        <v>66923</v>
       </c>
       <c r="H203" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8695,32 +8687,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C204" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C204" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D204" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E204" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F204" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 13 кг</t>
+          <t>Шпатлевка для влажных помещений ОРЕОЛ  4 кг</t>
         </is>
       </c>
       <c r="G204" s="30" t="n">
-        <v>5435</v>
+        <v>66924</v>
       </c>
       <c r="H204" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8733,32 +8725,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C205" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C205" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D205" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E205" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F205" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 3 кг</t>
+          <t>Шпатлевка интерьерная латексная ОРЕОЛ 1.5 кг</t>
         </is>
       </c>
       <c r="G205" s="30" t="n">
-        <v>5438</v>
+        <v>66526</v>
       </c>
       <c r="H205" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -8771,32 +8763,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C206" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C206" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D206" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E206" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F206" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 6.5 кг</t>
+          <t>Шпатлевка интерьерная латексная ОРЕОЛ 4 кг</t>
         </is>
       </c>
       <c r="G206" s="30" t="n">
-        <v>5440</v>
+        <v>66527</v>
       </c>
       <c r="H206" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8821,20 +8813,20 @@
       </c>
       <c r="E207" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F207" s="30" t="inlineStr">
         <is>
-          <t>Грунт-концентрат АКВАСТОП ОРЕОЛ 1 кг</t>
+          <t>Шпатлевка финишная ОРЕОЛ 1.5 кг</t>
         </is>
       </c>
       <c r="G207" s="30" t="n">
-        <v>66403</v>
+        <v>66524</v>
       </c>
       <c r="H207" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8859,20 +8851,20 @@
       </c>
       <c r="E208" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F208" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка бетон-контакт ОРЕОЛ 12 кг</t>
+          <t>Шпатлевка финишная ОРЕОЛ 4 кг</t>
         </is>
       </c>
       <c r="G208" s="30" t="n">
-        <v>66140</v>
+        <v>66525</v>
       </c>
       <c r="H208" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -8892,25 +8884,25 @@
       </c>
       <c r="D209" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E209" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F209" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка бетон-контакт ОРЕОЛ 3 кг</t>
+          <t>Шпатлевка ОРЕОЛ универсальная масляно-клеевая для внутренних работ ДИСКОНТ 1.5 кг</t>
         </is>
       </c>
       <c r="G209" s="30" t="n">
-        <v>66138</v>
+        <v>65828</v>
       </c>
       <c r="H209" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8930,25 +8922,25 @@
       </c>
       <c r="D210" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E210" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F210" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка бетон-контакт ОРЕОЛ 6 кг</t>
+          <t>Шпатлевка ОРЕОЛ универсальная масляно-клеевая для внутренних работ ДИСКОНТ 3.5 кг</t>
         </is>
       </c>
       <c r="G210" s="30" t="n">
-        <v>66139</v>
+        <v>88947</v>
       </c>
       <c r="H210" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8968,25 +8960,25 @@
       </c>
       <c r="D211" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Простокрашено! БАУ</t>
         </is>
       </c>
       <c r="E211" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F211" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка для влажных помещений ОРЕОЛ  1.5 кг</t>
+          <t>Грунтовка ГФ-021 Простокрашено серая 2.5 кг</t>
         </is>
       </c>
       <c r="G211" s="30" t="n">
-        <v>66923</v>
+        <v>85161</v>
       </c>
       <c r="H211" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -9006,21 +8998,21 @@
       </c>
       <c r="D212" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E212" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F212" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка для влажных помещений ОРЕОЛ  4 кг</t>
+          <t>Грунтовка ГФ-021 Расцвет серая 2.2 кг</t>
         </is>
       </c>
       <c r="G212" s="30" t="n">
-        <v>66924</v>
+        <v>11202</v>
       </c>
       <c r="H212" s="17" t="inlineStr">
         <is>
@@ -9044,21 +9036,21 @@
       </c>
       <c r="D213" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E213" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F213" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка интерьерная латексная ОРЕОЛ 1.5 кг</t>
+          <t>Грунтовка быстросохнущая ГФ-021 Расцвет красно-коричневая 2.5 кг</t>
         </is>
       </c>
       <c r="G213" s="30" t="n">
-        <v>66526</v>
+        <v>73562</v>
       </c>
       <c r="H213" s="17" t="inlineStr">
         <is>
@@ -9082,25 +9074,25 @@
       </c>
       <c r="D214" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E214" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F214" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка интерьерная латексная ОРЕОЛ 4 кг</t>
+          <t>Грунтовка быстросохнущая ГФ-021 Расцвет серая 1 кг</t>
         </is>
       </c>
       <c r="G214" s="30" t="n">
-        <v>66527</v>
+        <v>73565</v>
       </c>
       <c r="H214" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -9120,21 +9112,21 @@
       </c>
       <c r="D215" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E215" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F215" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка финишная ОРЕОЛ 1.5 кг</t>
+          <t>Грунтовка быстросохнущая ГФ-021 Расцвет серая 2.5 кг</t>
         </is>
       </c>
       <c r="G215" s="30" t="n">
-        <v>66524</v>
+        <v>73566</v>
       </c>
       <c r="H215" s="17" t="inlineStr">
         <is>
@@ -9143,240 +9135,240 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="17" t="n">
+      <c r="A216" s="19" t="n">
         <v>213</v>
       </c>
-      <c r="B216" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C216" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D216" s="30" t="inlineStr">
-        <is>
-          <t>Ореол</t>
-        </is>
-      </c>
-      <c r="E216" s="30" t="inlineStr">
-        <is>
-          <t>Шпатлёвки</t>
-        </is>
-      </c>
-      <c r="F216" s="30" t="inlineStr">
-        <is>
-          <t>Шпатлевка финишная ОРЕОЛ 4 кг</t>
-        </is>
-      </c>
-      <c r="G216" s="30" t="n">
-        <v>66525</v>
-      </c>
-      <c r="H216" s="17" t="inlineStr">
+      <c r="B216" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C216" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D216" s="31" t="inlineStr">
+        <is>
+          <t>PROFIWOOD</t>
+        </is>
+      </c>
+      <c r="E216" s="31" t="inlineStr">
+        <is>
+          <t>Лаки</t>
+        </is>
+      </c>
+      <c r="F216" s="31" t="inlineStr">
+        <is>
+          <t>Лак по дереву и камню PROFIWOOD ВД глянцевый 0.9 кг</t>
+        </is>
+      </c>
+      <c r="G216" s="31" t="n">
+        <v>64974</v>
+      </c>
+      <c r="H216" s="19" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="17" t="n">
+      <c r="A217" s="19" t="n">
         <v>214</v>
       </c>
-      <c r="B217" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C217" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D217" s="30" t="inlineStr">
-        <is>
-          <t>Ореол Дисконт</t>
-        </is>
-      </c>
-      <c r="E217" s="30" t="inlineStr">
-        <is>
-          <t>Шпатлёвки</t>
-        </is>
-      </c>
-      <c r="F217" s="30" t="inlineStr">
-        <is>
-          <t>Шпатлевка ОРЕОЛ универсальная масляно-клеевая для внутренних работ ДИСКОНТ 1.5 кг</t>
-        </is>
-      </c>
-      <c r="G217" s="30" t="n">
-        <v>65828</v>
-      </c>
-      <c r="H217" s="17" t="inlineStr">
+      <c r="B217" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C217" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D217" s="31" t="inlineStr">
+        <is>
+          <t>PROFIWOOD</t>
+        </is>
+      </c>
+      <c r="E217" s="31" t="inlineStr">
+        <is>
+          <t>Лаки</t>
+        </is>
+      </c>
+      <c r="F217" s="31" t="inlineStr">
+        <is>
+          <t>Лак по дереву и камню PROFIWOOD ВД глянцевый 2.2 кг</t>
+        </is>
+      </c>
+      <c r="G217" s="31" t="n">
+        <v>64975</v>
+      </c>
+      <c r="H217" s="19" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="19" t="n">
+        <v>215</v>
+      </c>
+      <c r="B218" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C218" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D218" s="31" t="inlineStr">
+        <is>
+          <t>PROFIWOOD</t>
+        </is>
+      </c>
+      <c r="E218" s="31" t="inlineStr">
+        <is>
+          <t>Лаки</t>
+        </is>
+      </c>
+      <c r="F218" s="31" t="inlineStr">
+        <is>
+          <t>Лак-антисептик для бань и саун PROFIWOOD ВД 0.9 кг</t>
+        </is>
+      </c>
+      <c r="G218" s="31" t="n">
+        <v>6493</v>
+      </c>
+      <c r="H218" s="19" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="17" t="n">
-        <v>215</v>
-      </c>
-      <c r="B218" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C218" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D218" s="30" t="inlineStr">
-        <is>
-          <t>Ореол Дисконт</t>
-        </is>
-      </c>
-      <c r="E218" s="30" t="inlineStr">
-        <is>
-          <t>Шпатлёвки</t>
-        </is>
-      </c>
-      <c r="F218" s="30" t="inlineStr">
-        <is>
-          <t>Шпатлевка ОРЕОЛ универсальная масляно-клеевая для внутренних работ ДИСКОНТ 3.5 кг</t>
-        </is>
-      </c>
-      <c r="G218" s="30" t="n">
-        <v>88947</v>
-      </c>
-      <c r="H218" s="17" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="19" t="n">
+        <v>216</v>
+      </c>
+      <c r="B219" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C219" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D219" s="31" t="inlineStr">
+        <is>
+          <t>PROFIWOOD</t>
+        </is>
+      </c>
+      <c r="E219" s="31" t="inlineStr">
+        <is>
+          <t>Лаки</t>
+        </is>
+      </c>
+      <c r="F219" s="31" t="inlineStr">
+        <is>
+          <t>Лак-антисептик для бань и саун PROFIWOOD ВД 2.5 кг</t>
+        </is>
+      </c>
+      <c r="G219" s="31" t="n">
+        <v>6494</v>
+      </c>
+      <c r="H219" s="19" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="17" t="n">
-        <v>216</v>
-      </c>
-      <c r="B219" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C219" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D219" s="30" t="inlineStr">
-        <is>
-          <t>Простокрашено! БАУ</t>
-        </is>
-      </c>
-      <c r="E219" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовки</t>
-        </is>
-      </c>
-      <c r="F219" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовка ГФ-021 Простокрашено серая 2.5 кг</t>
-        </is>
-      </c>
-      <c r="G219" s="30" t="n">
-        <v>85161</v>
-      </c>
-      <c r="H219" s="17" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="19" t="n">
+        <v>217</v>
+      </c>
+      <c r="B220" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C220" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D220" s="31" t="inlineStr">
+        <is>
+          <t>PROFIWOOD</t>
+        </is>
+      </c>
+      <c r="E220" s="31" t="inlineStr">
+        <is>
+          <t>Растворы для защиты древесины</t>
+        </is>
+      </c>
+      <c r="F220" s="31" t="inlineStr">
+        <is>
+          <t>Раствор водный защитного средства для древесины ФБС-255 10 л 10 кг</t>
+        </is>
+      </c>
+      <c r="G220" s="31" t="n">
+        <v>83757</v>
+      </c>
+      <c r="H220" s="19" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="17" t="n">
-        <v>217</v>
-      </c>
-      <c r="B220" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C220" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D220" s="30" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E220" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовки</t>
-        </is>
-      </c>
-      <c r="F220" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовка ГФ-021 Расцвет серая 2.2 кг</t>
-        </is>
-      </c>
-      <c r="G220" s="30" t="n">
-        <v>11202</v>
-      </c>
-      <c r="H220" s="17" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="19" t="n">
+        <v>218</v>
+      </c>
+      <c r="B221" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C221" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
+        </is>
+      </c>
+      <c r="D221" s="31" t="inlineStr">
+        <is>
+          <t>AvantGarde</t>
+        </is>
+      </c>
+      <c r="E221" s="31" t="inlineStr">
+        <is>
+          <t>Декоративные составы</t>
+        </is>
+      </c>
+      <c r="F221" s="31" t="inlineStr">
+        <is>
+          <t>Защитно-декоративное покрытие для дерева AvantGarde белое</t>
+        </is>
+      </c>
+      <c r="G221" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="19" t="inlineStr">
         <is>
           <t>С</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="17" t="n">
-        <v>218</v>
-      </c>
-      <c r="B221" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C221" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D221" s="30" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E221" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовки</t>
-        </is>
-      </c>
-      <c r="F221" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовка быстросохнущая ГФ-021 Расцвет красно-коричневая 2.5 кг</t>
-        </is>
-      </c>
-      <c r="G221" s="30" t="n">
-        <v>73562</v>
-      </c>
-      <c r="H221" s="17" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-    </row>
     <row r="222">
-      <c r="A222" s="17" t="n">
+      <c r="A222" s="19" t="n">
         <v>219</v>
       </c>
-      <c r="B222" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
+      <c r="B222" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
         </is>
       </c>
       <c r="C222" s="29" t="inlineStr">
@@ -9384,37 +9376,37 @@
           <t>Органическая</t>
         </is>
       </c>
-      <c r="D222" s="30" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E222" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовки</t>
-        </is>
-      </c>
-      <c r="F222" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовка быстросохнущая ГФ-021 Расцвет серая 1 кг</t>
-        </is>
-      </c>
-      <c r="G222" s="30" t="n">
-        <v>73565</v>
-      </c>
-      <c r="H222" s="17" t="inlineStr">
-        <is>
-          <t>В</t>
+      <c r="D222" s="31" t="inlineStr">
+        <is>
+          <t>AvantGarde</t>
+        </is>
+      </c>
+      <c r="E222" s="31" t="inlineStr">
+        <is>
+          <t>Декоративные составы</t>
+        </is>
+      </c>
+      <c r="F222" s="31" t="inlineStr">
+        <is>
+          <t>Защитно-декоративное покрытие для дерева AvantGarde олива</t>
+        </is>
+      </c>
+      <c r="G222" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" s="19" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="17" t="n">
+      <c r="A223" s="19" t="n">
         <v>220</v>
       </c>
-      <c r="B223" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
+      <c r="B223" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
         </is>
       </c>
       <c r="C223" s="29" t="inlineStr">
@@ -9422,37 +9414,37 @@
           <t>Органическая</t>
         </is>
       </c>
-      <c r="D223" s="30" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E223" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовки</t>
-        </is>
-      </c>
-      <c r="F223" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовка быстросохнущая ГФ-021 Расцвет серая 2.5 кг</t>
-        </is>
-      </c>
-      <c r="G223" s="30" t="n">
-        <v>73566</v>
-      </c>
-      <c r="H223" s="17" t="inlineStr">
-        <is>
-          <t>А</t>
+      <c r="D223" s="31" t="inlineStr">
+        <is>
+          <t>AvantGarde</t>
+        </is>
+      </c>
+      <c r="E223" s="31" t="inlineStr">
+        <is>
+          <t>Декоративные составы</t>
+        </is>
+      </c>
+      <c r="F223" s="31" t="inlineStr">
+        <is>
+          <t>Защитно-декоративное покрытие для дерева AvantGarde сосна</t>
+        </is>
+      </c>
+      <c r="G223" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" s="19" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="17" t="n">
+      <c r="A224" s="19" t="n">
         <v>221</v>
       </c>
-      <c r="B224" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
+      <c r="B224" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
         </is>
       </c>
       <c r="C224" s="29" t="inlineStr">
@@ -9460,27 +9452,27 @@
           <t>Органическая</t>
         </is>
       </c>
-      <c r="D224" s="30" t="inlineStr">
-        <is>
-          <t>СТРОЙКОМПЛЕКТ</t>
-        </is>
-      </c>
-      <c r="E224" s="30" t="inlineStr">
-        <is>
-          <t>Краски</t>
-        </is>
-      </c>
-      <c r="F224" s="30" t="inlineStr">
-        <is>
-          <t>Краска интерьерная СТРОЙКОМПЛЕКТ 25 кг</t>
-        </is>
-      </c>
-      <c r="G224" s="30" t="n">
-        <v>73171</v>
-      </c>
-      <c r="H224" s="17" t="inlineStr">
-        <is>
-          <t>А</t>
+      <c r="D224" s="31" t="inlineStr">
+        <is>
+          <t>AvantGarde</t>
+        </is>
+      </c>
+      <c r="E224" s="31" t="inlineStr">
+        <is>
+          <t>Лаки</t>
+        </is>
+      </c>
+      <c r="F224" s="31" t="inlineStr">
+        <is>
+          <t>Лак высокой твердости паркетный AvantGarde глянцевый бесцветный</t>
+        </is>
+      </c>
+      <c r="G224" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" s="19" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9493,32 +9485,32 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C225" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C225" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D225" s="31" t="inlineStr">
         <is>
-          <t>NoName</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E225" s="31" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Лаки</t>
         </is>
       </c>
       <c r="F225" s="31" t="inlineStr">
         <is>
-          <t>Краска ВД для садовых деревьев 3 кг</t>
+          <t>Лак высокой твердости паркетный AvantGarde полуматовый бесцветный</t>
         </is>
       </c>
       <c r="G225" s="31" t="n">
-        <v>63180</v>
+        <v>0</v>
       </c>
       <c r="H225" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9531,14 +9523,14 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C226" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C226" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D226" s="31" t="inlineStr">
         <is>
-          <t>PROFIWOOD</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E226" s="31" t="inlineStr">
@@ -9548,15 +9540,15 @@
       </c>
       <c r="F226" s="31" t="inlineStr">
         <is>
-          <t>Лак по дереву и камню PROFIWOOD ВД глянцевый 0.9 кг</t>
+          <t>Лак высокой твердости яхтный AvantGarde глянцевый бесцветный</t>
         </is>
       </c>
       <c r="G226" s="31" t="n">
-        <v>64974</v>
+        <v>0</v>
       </c>
       <c r="H226" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9569,14 +9561,14 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C227" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C227" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D227" s="31" t="inlineStr">
         <is>
-          <t>PROFIWOOD</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E227" s="31" t="inlineStr">
@@ -9586,15 +9578,15 @@
       </c>
       <c r="F227" s="31" t="inlineStr">
         <is>
-          <t>Лак по дереву и камню PROFIWOOD ВД глянцевый 2.2 кг</t>
+          <t>Лак высокой твердости яхтный AvantGarde полуматовый бесцветный</t>
         </is>
       </c>
       <c r="G227" s="31" t="n">
-        <v>64975</v>
+        <v>0</v>
       </c>
       <c r="H227" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9607,9 +9599,9 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C228" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C228" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D228" s="31" t="inlineStr">
@@ -9619,20 +9611,20 @@
       </c>
       <c r="E228" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F228" s="31" t="inlineStr">
         <is>
-          <t>Лак-антисептик для бань и саун PROFIWOOD ВД 0.9 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD бесцветный 0.7 кг</t>
         </is>
       </c>
       <c r="G228" s="31" t="n">
-        <v>6493</v>
+        <v>66992</v>
       </c>
       <c r="H228" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9645,9 +9637,9 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C229" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C229" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D229" s="31" t="inlineStr">
@@ -9657,20 +9649,20 @@
       </c>
       <c r="E229" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F229" s="31" t="inlineStr">
         <is>
-          <t>Лак-антисептик для бань и саун PROFIWOOD ВД 2.5 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD бесцветный 2.4 кг</t>
         </is>
       </c>
       <c r="G229" s="31" t="n">
-        <v>6494</v>
+        <v>66993</v>
       </c>
       <c r="H229" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9683,9 +9675,9 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C230" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C230" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D230" s="31" t="inlineStr">
@@ -9695,20 +9687,20 @@
       </c>
       <c r="E230" s="31" t="inlineStr">
         <is>
-          <t>Растворы для защиты древесины</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F230" s="31" t="inlineStr">
         <is>
-          <t>Раствор водный защитного средства для древесины ФБС-255 10 л 10 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD бук 0.7 кг</t>
         </is>
       </c>
       <c r="G230" s="31" t="n">
-        <v>83757</v>
+        <v>67017</v>
       </c>
       <c r="H230" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9738,11 +9730,11 @@
       </c>
       <c r="F231" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD бесцветный 0.7 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD дуб 0.7 кг</t>
         </is>
       </c>
       <c r="G231" s="31" t="n">
-        <v>66992</v>
+        <v>67042</v>
       </c>
       <c r="H231" s="19" t="inlineStr">
         <is>
@@ -9776,11 +9768,11 @@
       </c>
       <c r="F232" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD бесцветный 2.4 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD красное дерево 0.7 кг</t>
         </is>
       </c>
       <c r="G232" s="31" t="n">
-        <v>66993</v>
+        <v>67032</v>
       </c>
       <c r="H232" s="19" t="inlineStr">
         <is>
@@ -9814,11 +9806,11 @@
       </c>
       <c r="F233" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD бук 0.7 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD красное дерево 2.4 кг</t>
         </is>
       </c>
       <c r="G233" s="31" t="n">
-        <v>67017</v>
+        <v>67033</v>
       </c>
       <c r="H233" s="19" t="inlineStr">
         <is>
@@ -9852,11 +9844,11 @@
       </c>
       <c r="F234" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD дуб 0.7 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD орегон 0.7 кг</t>
         </is>
       </c>
       <c r="G234" s="31" t="n">
-        <v>67042</v>
+        <v>67023</v>
       </c>
       <c r="H234" s="19" t="inlineStr">
         <is>
@@ -9890,11 +9882,11 @@
       </c>
       <c r="F235" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD красное дерево 0.7 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD орех 0.7 кг</t>
         </is>
       </c>
       <c r="G235" s="31" t="n">
-        <v>67032</v>
+        <v>67026</v>
       </c>
       <c r="H235" s="19" t="inlineStr">
         <is>
@@ -9928,11 +9920,11 @@
       </c>
       <c r="F236" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD красное дерево 2.4 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD орех 2.4 кг</t>
         </is>
       </c>
       <c r="G236" s="31" t="n">
-        <v>67033</v>
+        <v>67027</v>
       </c>
       <c r="H236" s="19" t="inlineStr">
         <is>
@@ -9966,15 +9958,15 @@
       </c>
       <c r="F237" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD орегон 0.7 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD палисандр 0.7 кг</t>
         </is>
       </c>
       <c r="G237" s="31" t="n">
-        <v>67023</v>
+        <v>67029</v>
       </c>
       <c r="H237" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -10004,15 +9996,15 @@
       </c>
       <c r="F238" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD орех 0.7 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD палисандр 2.4 кг</t>
         </is>
       </c>
       <c r="G238" s="31" t="n">
-        <v>67026</v>
+        <v>67030</v>
       </c>
       <c r="H238" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -10042,11 +10034,11 @@
       </c>
       <c r="F239" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD орех 2.4 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD сосна 0.7 кг</t>
         </is>
       </c>
       <c r="G239" s="31" t="n">
-        <v>67027</v>
+        <v>67014</v>
       </c>
       <c r="H239" s="19" t="inlineStr">
         <is>
@@ -10080,15 +10072,15 @@
       </c>
       <c r="F240" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD палисандр 0.7 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD сосна 2.4 кг</t>
         </is>
       </c>
       <c r="G240" s="31" t="n">
-        <v>67029</v>
+        <v>67015</v>
       </c>
       <c r="H240" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -10118,15 +10110,15 @@
       </c>
       <c r="F241" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD палисандр 2.4 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD тик 0.7 кг</t>
         </is>
       </c>
       <c r="G241" s="31" t="n">
-        <v>67030</v>
+        <v>67035</v>
       </c>
       <c r="H241" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -10156,11 +10148,11 @@
       </c>
       <c r="F242" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD сосна 0.7 кг</t>
+          <t>Антисептик лаковый тонирующий PROFIWOOD тик 2.4 кг</t>
         </is>
       </c>
       <c r="G242" s="31" t="n">
-        <v>67014</v>
+        <v>67036</v>
       </c>
       <c r="H242" s="19" t="inlineStr">
         <is>
@@ -10189,20 +10181,20 @@
       </c>
       <c r="E243" s="31" t="inlineStr">
         <is>
-          <t>Декоративные составы</t>
+          <t>Растворы для защиты древесины</t>
         </is>
       </c>
       <c r="F243" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD сосна 2.4 кг</t>
+          <t>Антисептик универсальный против плесени и грибка (Антиплесень) 10 кг</t>
         </is>
       </c>
       <c r="G243" s="31" t="n">
-        <v>67015</v>
+        <v>71283</v>
       </c>
       <c r="H243" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -10227,20 +10219,20 @@
       </c>
       <c r="E244" s="31" t="inlineStr">
         <is>
-          <t>Декоративные составы</t>
+          <t>Растворы для защиты древесины</t>
         </is>
       </c>
       <c r="F244" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD тик 0.7 кг</t>
+          <t>Антисептик универсальный против плесени и грибка (Антиплесень) 5 кг</t>
         </is>
       </c>
       <c r="G244" s="31" t="n">
-        <v>67035</v>
+        <v>71282</v>
       </c>
       <c r="H244" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -10270,11 +10262,11 @@
       </c>
       <c r="F245" s="31" t="inlineStr">
         <is>
-          <t>Антисептик лаковый тонирующий PROFIWOOD тик 2.4 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD красное дерево 0.7 кг</t>
         </is>
       </c>
       <c r="G245" s="31" t="n">
-        <v>67036</v>
+        <v>72627</v>
       </c>
       <c r="H245" s="19" t="inlineStr">
         <is>
@@ -10303,20 +10295,20 @@
       </c>
       <c r="E246" s="31" t="inlineStr">
         <is>
-          <t>Растворы для защиты древесины</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F246" s="31" t="inlineStr">
         <is>
-          <t>Антисептик универсальный против плесени и грибка (Антиплесень) 10 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD махагон 0.7 кг</t>
         </is>
       </c>
       <c r="G246" s="31" t="n">
-        <v>71283</v>
+        <v>72626</v>
       </c>
       <c r="H246" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -10341,20 +10333,20 @@
       </c>
       <c r="E247" s="31" t="inlineStr">
         <is>
-          <t>Растворы для защиты древесины</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F247" s="31" t="inlineStr">
         <is>
-          <t>Антисептик универсальный против плесени и грибка (Антиплесень) 5 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD орех 0.7 кг</t>
         </is>
       </c>
       <c r="G247" s="31" t="n">
-        <v>71282</v>
+        <v>72622</v>
       </c>
       <c r="H247" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -10384,15 +10376,15 @@
       </c>
       <c r="F248" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD красное дерево 0.7 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD орех 2.3 кг</t>
         </is>
       </c>
       <c r="G248" s="31" t="n">
-        <v>72627</v>
+        <v>72636</v>
       </c>
       <c r="H248" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -10422,15 +10414,15 @@
       </c>
       <c r="F249" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD махагон 0.7 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD палисандр 0.7 кг</t>
         </is>
       </c>
       <c r="G249" s="31" t="n">
-        <v>72626</v>
+        <v>72628</v>
       </c>
       <c r="H249" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -10460,15 +10452,15 @@
       </c>
       <c r="F250" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD орех 0.7 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD палисандр 2.3 кг</t>
         </is>
       </c>
       <c r="G250" s="31" t="n">
-        <v>72622</v>
+        <v>72660</v>
       </c>
       <c r="H250" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -10498,15 +10490,15 @@
       </c>
       <c r="F251" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD орех 2.3 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD рябина 0.7 кг</t>
         </is>
       </c>
       <c r="G251" s="31" t="n">
-        <v>72636</v>
+        <v>72625</v>
       </c>
       <c r="H251" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -10536,11 +10528,11 @@
       </c>
       <c r="F252" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD палисандр 0.7 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD сосна 0.7 кг</t>
         </is>
       </c>
       <c r="G252" s="31" t="n">
-        <v>72628</v>
+        <v>72619</v>
       </c>
       <c r="H252" s="19" t="inlineStr">
         <is>
@@ -10574,15 +10566,15 @@
       </c>
       <c r="F253" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD палисандр 2.3 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD сосна 2.3 кг</t>
         </is>
       </c>
       <c r="G253" s="31" t="n">
-        <v>72660</v>
+        <v>72634</v>
       </c>
       <c r="H253" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -10612,15 +10604,15 @@
       </c>
       <c r="F254" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD рябина 0.7 кг</t>
+          <t>Защитно-декоративное покрытие для древесины PROFIWOOD тик 0.7 кг</t>
         </is>
       </c>
       <c r="G254" s="31" t="n">
-        <v>72625</v>
+        <v>72624</v>
       </c>
       <c r="H254" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -10645,16 +10637,16 @@
       </c>
       <c r="E255" s="31" t="inlineStr">
         <is>
-          <t>Декоративные составы</t>
+          <t>Лаки</t>
         </is>
       </c>
       <c r="F255" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD сосна 0.7 кг</t>
+          <t>Лак паркетный PROFIWOOD глянцевый 0.7 кг</t>
         </is>
       </c>
       <c r="G255" s="31" t="n">
-        <v>72619</v>
+        <v>6309</v>
       </c>
       <c r="H255" s="19" t="inlineStr">
         <is>
@@ -10683,16 +10675,16 @@
       </c>
       <c r="E256" s="31" t="inlineStr">
         <is>
-          <t>Декоративные составы</t>
+          <t>Лаки</t>
         </is>
       </c>
       <c r="F256" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD сосна 2.3 кг</t>
+          <t>Лак паркетный PROFIWOOD глянцевый 2.4 кг 6 шт.</t>
         </is>
       </c>
       <c r="G256" s="31" t="n">
-        <v>72634</v>
+        <v>62238</v>
       </c>
       <c r="H256" s="19" t="inlineStr">
         <is>
@@ -10721,16 +10713,16 @@
       </c>
       <c r="E257" s="31" t="inlineStr">
         <is>
-          <t>Декоративные составы</t>
+          <t>Лаки</t>
         </is>
       </c>
       <c r="F257" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для древесины PROFIWOOD тик 0.7 кг</t>
+          <t>Лак паркетный PROFIWOOD матовый 0.7 кг</t>
         </is>
       </c>
       <c r="G257" s="31" t="n">
-        <v>72624</v>
+        <v>6313</v>
       </c>
       <c r="H257" s="19" t="inlineStr">
         <is>
@@ -10764,15 +10756,15 @@
       </c>
       <c r="F258" s="31" t="inlineStr">
         <is>
-          <t>Лак паркетный PROFIWOOD глянцевый 0.7 кг</t>
+          <t>Лак яхтный PROFIWOOD глянцевый 0.7 кг</t>
         </is>
       </c>
       <c r="G258" s="31" t="n">
-        <v>6309</v>
+        <v>6463</v>
       </c>
       <c r="H258" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -10802,15 +10794,15 @@
       </c>
       <c r="F259" s="31" t="inlineStr">
         <is>
-          <t>Лак паркетный PROFIWOOD глянцевый 2.4 кг 6 шт.</t>
+          <t>Лак яхтный PROFIWOOD глянцевый 2.4 кг 6 шт.</t>
         </is>
       </c>
       <c r="G259" s="31" t="n">
-        <v>62238</v>
+        <v>62103</v>
       </c>
       <c r="H259" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -10840,11 +10832,11 @@
       </c>
       <c r="F260" s="31" t="inlineStr">
         <is>
-          <t>Лак паркетный PROFIWOOD матовый 0.7 кг</t>
+          <t>Лак яхтный PROFIWOOD матовый 0.7 кг</t>
         </is>
       </c>
       <c r="G260" s="31" t="n">
-        <v>6313</v>
+        <v>63496</v>
       </c>
       <c r="H260" s="19" t="inlineStr">
         <is>
@@ -10878,15 +10870,15 @@
       </c>
       <c r="F261" s="31" t="inlineStr">
         <is>
-          <t>Лак яхтный PROFIWOOD глянцевый 0.7 кг</t>
+          <t>Лак яхтный PROFIWOOD матовый 2.4 кг</t>
         </is>
       </c>
       <c r="G261" s="31" t="n">
-        <v>6463</v>
+        <v>63497</v>
       </c>
       <c r="H261" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -10916,15 +10908,15 @@
       </c>
       <c r="F262" s="31" t="inlineStr">
         <is>
-          <t>Лак яхтный PROFIWOOD глянцевый 2.4 кг 6 шт.</t>
+          <t>Лак яхтный PROFIWOOD полуматовый 0.7 кг</t>
         </is>
       </c>
       <c r="G262" s="31" t="n">
-        <v>62103</v>
+        <v>6465</v>
       </c>
       <c r="H262" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -10949,20 +10941,20 @@
       </c>
       <c r="E263" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F263" s="31" t="inlineStr">
         <is>
-          <t>Лак яхтный PROFIWOOD матовый 0.7 кг</t>
+          <t>Масло для защиты полка PROFIWOOD 0.176 кг</t>
         </is>
       </c>
       <c r="G263" s="31" t="n">
-        <v>63496</v>
+        <v>67117</v>
       </c>
       <c r="H263" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10974,7 @@
       </c>
       <c r="D264" s="31" t="inlineStr">
         <is>
-          <t>PROFIWOOD</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E264" s="31" t="inlineStr">
@@ -10992,11 +10984,11 @@
       </c>
       <c r="F264" s="31" t="inlineStr">
         <is>
-          <t>Лак яхтный PROFIWOOD матовый 2.4 кг</t>
+          <t>Лак Расцвет для наружных работ алкидный 0.7 кг</t>
         </is>
       </c>
       <c r="G264" s="31" t="n">
-        <v>63497</v>
+        <v>86736</v>
       </c>
       <c r="H264" s="19" t="inlineStr">
         <is>
@@ -11020,7 +11012,7 @@
       </c>
       <c r="D265" s="31" t="inlineStr">
         <is>
-          <t>PROFIWOOD</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E265" s="31" t="inlineStr">
@@ -11030,127 +11022,127 @@
       </c>
       <c r="F265" s="31" t="inlineStr">
         <is>
-          <t>Лак яхтный PROFIWOOD полуматовый 0.7 кг</t>
+          <t>Лак Расцвет для наружных работ алкидный 1.6 кг</t>
         </is>
       </c>
       <c r="G265" s="31" t="n">
-        <v>6465</v>
+        <v>86737</v>
       </c>
       <c r="H265" s="19" t="inlineStr">
         <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="21" t="n">
+        <v>263</v>
+      </c>
+      <c r="B266" s="32" t="inlineStr">
+        <is>
+          <t>Пол</t>
+        </is>
+      </c>
+      <c r="C266" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D266" s="32" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E266" s="32" t="inlineStr">
+        <is>
+          <t>Эмали ВДАК</t>
+        </is>
+      </c>
+      <c r="F266" s="32" t="inlineStr">
+        <is>
+          <t>Эмаль для пола акриловая Ореол полуматовая венге 0.9 кг</t>
+        </is>
+      </c>
+      <c r="G266" s="32" t="n">
+        <v>73369</v>
+      </c>
+      <c r="H266" s="21" t="inlineStr">
+        <is>
           <t>С</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="19" t="n">
-        <v>263</v>
-      </c>
-      <c r="B266" s="31" t="inlineStr">
-        <is>
-          <t>Дерево</t>
-        </is>
-      </c>
-      <c r="C266" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D266" s="31" t="inlineStr">
-        <is>
-          <t>PROFIWOOD</t>
-        </is>
-      </c>
-      <c r="E266" s="31" t="inlineStr">
-        <is>
-          <t>Декоративные составы</t>
-        </is>
-      </c>
-      <c r="F266" s="31" t="inlineStr">
-        <is>
-          <t>Масло для защиты полка PROFIWOOD 0.176 кг</t>
-        </is>
-      </c>
-      <c r="G266" s="31" t="n">
-        <v>67117</v>
-      </c>
-      <c r="H266" s="19" t="inlineStr">
-        <is>
-          <t>С</t>
-        </is>
-      </c>
-    </row>
     <row r="267">
-      <c r="A267" s="19" t="n">
+      <c r="A267" s="21" t="n">
         <v>264</v>
       </c>
-      <c r="B267" s="31" t="inlineStr">
-        <is>
-          <t>Дерево</t>
-        </is>
-      </c>
-      <c r="C267" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D267" s="31" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E267" s="31" t="inlineStr">
-        <is>
-          <t>Лаки</t>
-        </is>
-      </c>
-      <c r="F267" s="31" t="inlineStr">
-        <is>
-          <t>Лак Расцвет для наружных работ алкидный 0.7 кг</t>
-        </is>
-      </c>
-      <c r="G267" s="31" t="n">
-        <v>86736</v>
-      </c>
-      <c r="H267" s="19" t="inlineStr">
+      <c r="B267" s="32" t="inlineStr">
+        <is>
+          <t>Пол</t>
+        </is>
+      </c>
+      <c r="C267" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D267" s="32" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E267" s="32" t="inlineStr">
+        <is>
+          <t>Эмали ВДАК</t>
+        </is>
+      </c>
+      <c r="F267" s="32" t="inlineStr">
+        <is>
+          <t>Эмаль для пола акриловая Ореол полуматовая венге 2.3 кг</t>
+        </is>
+      </c>
+      <c r="G267" s="32" t="n">
+        <v>73370</v>
+      </c>
+      <c r="H267" s="21" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="19" t="n">
+      <c r="A268" s="21" t="n">
         <v>265</v>
       </c>
-      <c r="B268" s="31" t="inlineStr">
-        <is>
-          <t>Дерево</t>
-        </is>
-      </c>
-      <c r="C268" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D268" s="31" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E268" s="31" t="inlineStr">
-        <is>
-          <t>Лаки</t>
-        </is>
-      </c>
-      <c r="F268" s="31" t="inlineStr">
-        <is>
-          <t>Лак Расцвет для наружных работ алкидный 1.6 кг</t>
-        </is>
-      </c>
-      <c r="G268" s="31" t="n">
-        <v>86737</v>
-      </c>
-      <c r="H268" s="19" t="inlineStr">
+      <c r="B268" s="32" t="inlineStr">
+        <is>
+          <t>Пол</t>
+        </is>
+      </c>
+      <c r="C268" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D268" s="32" t="inlineStr">
+        <is>
+          <t>Ореол</t>
+        </is>
+      </c>
+      <c r="E268" s="32" t="inlineStr">
+        <is>
+          <t>Эмали ВДАК</t>
+        </is>
+      </c>
+      <c r="F268" s="32" t="inlineStr">
+        <is>
+          <t>Эмаль для пола акриловая Ореол полуматовая желто-коричневая 0.9 кг</t>
+        </is>
+      </c>
+      <c r="G268" s="32" t="n">
+        <v>73363</v>
+      </c>
+      <c r="H268" s="21" t="inlineStr">
         <is>
           <t>В</t>
         </is>
@@ -11182,15 +11174,15 @@
       </c>
       <c r="F269" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая венге 0.9 кг</t>
+          <t>Эмаль для пола акриловая Ореол полуматовая желто-коричневая 2.3 кг</t>
         </is>
       </c>
       <c r="G269" s="32" t="n">
-        <v>73369</v>
+        <v>73364</v>
       </c>
       <c r="H269" s="21" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -11220,15 +11212,15 @@
       </c>
       <c r="F270" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая венге 2.3 кг</t>
+          <t>Эмаль для пола акриловая Ореол полуматовая золотисто-коричневая 0.9 кг</t>
         </is>
       </c>
       <c r="G270" s="32" t="n">
-        <v>73370</v>
+        <v>73365</v>
       </c>
       <c r="H270" s="21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -11258,15 +11250,15 @@
       </c>
       <c r="F271" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая желто-коричневая 0.9 кг</t>
+          <t>Эмаль для пола акриловая Ореол полуматовая золотисто-коричневая 2.3 кг</t>
         </is>
       </c>
       <c r="G271" s="32" t="n">
-        <v>73363</v>
+        <v>73366</v>
       </c>
       <c r="H271" s="21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -11296,15 +11288,15 @@
       </c>
       <c r="F272" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая желто-коричневая 2.3 кг</t>
+          <t>Эмаль для пола акриловая Ореол полуматовая красно-коричневая 0.9 кг</t>
         </is>
       </c>
       <c r="G272" s="32" t="n">
-        <v>73364</v>
+        <v>73367</v>
       </c>
       <c r="H272" s="21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -11334,15 +11326,15 @@
       </c>
       <c r="F273" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая золотисто-коричневая 0.9 кг</t>
+          <t>Эмаль для пола акриловая Ореол полуматовая красно-коричневая 2.3 кг</t>
         </is>
       </c>
       <c r="G273" s="32" t="n">
-        <v>73365</v>
+        <v>73368</v>
       </c>
       <c r="H273" s="21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -11372,15 +11364,15 @@
       </c>
       <c r="F274" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая золотисто-коричневая 2.3 кг</t>
+          <t>Эмаль для пола акриловая Ореол полуматовая тёмно-серая 0.9 кг</t>
         </is>
       </c>
       <c r="G274" s="32" t="n">
-        <v>73366</v>
+        <v>78185</v>
       </c>
       <c r="H274" s="21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -11410,15 +11402,15 @@
       </c>
       <c r="F275" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая красно-коричневая 0.9 кг</t>
+          <t>Эмаль для пола акриловая Ореол полуматовая тёмно-серая 2.3 кг</t>
         </is>
       </c>
       <c r="G275" s="32" t="n">
-        <v>73367</v>
+        <v>78186</v>
       </c>
       <c r="H275" s="21" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -11448,15 +11440,15 @@
       </c>
       <c r="F276" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая красно-коричневая 2.3 кг</t>
+          <t>Эмаль по пластику ОРЕОЛ полуматовая 0.9 кг</t>
         </is>
       </c>
       <c r="G276" s="32" t="n">
-        <v>73368</v>
+        <v>70707</v>
       </c>
       <c r="H276" s="21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -11469,28 +11461,28 @@
           <t>Пол</t>
         </is>
       </c>
-      <c r="C277" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C277" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D277" s="32" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Простокрашено! БАУ</t>
         </is>
       </c>
       <c r="E277" s="32" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Эмали Алкидные для пола</t>
         </is>
       </c>
       <c r="F277" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая тёмно-серая 0.9 кг</t>
+          <t>Эмаль "Простокрашено!" для пола жёлто-коричневая БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G277" s="32" t="n">
-        <v>78185</v>
+        <v>81336</v>
       </c>
       <c r="H277" s="21" t="inlineStr">
         <is>
@@ -11507,32 +11499,32 @@
           <t>Пол</t>
         </is>
       </c>
-      <c r="C278" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C278" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D278" s="32" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Простокрашено! БАУ</t>
         </is>
       </c>
       <c r="E278" s="32" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Эмали Алкидные для пола</t>
         </is>
       </c>
       <c r="F278" s="32" t="inlineStr">
         <is>
-          <t>Эмаль для пола акриловая Ореол полуматовая тёмно-серая 2.3 кг</t>
+          <t>Эмаль "Простокрашено!" для пола жёлто-коричневая БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G278" s="32" t="n">
-        <v>78186</v>
+        <v>85191</v>
       </c>
       <c r="H278" s="21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -11545,32 +11537,32 @@
           <t>Пол</t>
         </is>
       </c>
-      <c r="C279" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C279" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D279" s="32" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Простокрашено! БАУ</t>
         </is>
       </c>
       <c r="E279" s="32" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Эмали Алкидные для пола</t>
         </is>
       </c>
       <c r="F279" s="32" t="inlineStr">
         <is>
-          <t>Эмаль по пластику ОРЕОЛ полуматовая 0.9 кг</t>
+          <t>Эмаль "Простокрашено!" для пола жёлто-коричневая БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G279" s="32" t="n">
-        <v>70707</v>
+        <v>7633</v>
       </c>
       <c r="H279" s="21" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -11600,11 +11592,11 @@
       </c>
       <c r="F280" s="32" t="inlineStr">
         <is>
-          <t>Эмаль "Простокрашено!" для пола жёлто-коричневая БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль "Простокрашено!" для пола золотистая БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G280" s="32" t="n">
-        <v>81336</v>
+        <v>72942</v>
       </c>
       <c r="H280" s="21" t="inlineStr">
         <is>
@@ -11638,11 +11630,11 @@
       </c>
       <c r="F281" s="32" t="inlineStr">
         <is>
-          <t>Эмаль "Простокрашено!" для пола жёлто-коричневая БАУЦЕНТР 1.8 кг</t>
+          <t>Эмаль "Простокрашено!" для пола золотисто-коричневая БАУЦЕНТР 0.8 кг</t>
         </is>
       </c>
       <c r="G281" s="32" t="n">
-        <v>85191</v>
+        <v>81337</v>
       </c>
       <c r="H281" s="21" t="inlineStr">
         <is>
@@ -11676,11 +11668,11 @@
       </c>
       <c r="F282" s="32" t="inlineStr">
         <is>
-          <t>Эмаль "Простокрашено!" для пола жёлто-коричневая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль "Простокрашено!" для пола золотисто-коричневая БАУЦЕНТР 1.8 кг</t>
         </is>
       </c>
       <c r="G282" s="32" t="n">
-        <v>7633</v>
+        <v>85192</v>
       </c>
       <c r="H282" s="21" t="inlineStr">
         <is>
@@ -11714,15 +11706,15 @@
       </c>
       <c r="F283" s="32" t="inlineStr">
         <is>
-          <t>Эмаль "Простокрашено!" для пола золотистая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль "Простокрашено!" для пола золотисто-коричневая БАУЦЕНТР 2.7 кг</t>
         </is>
       </c>
       <c r="G283" s="32" t="n">
-        <v>72942</v>
+        <v>7652</v>
       </c>
       <c r="H283" s="21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11734,7 @@
       </c>
       <c r="D284" s="32" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E284" s="32" t="inlineStr">
@@ -11752,15 +11744,15 @@
       </c>
       <c r="F284" s="32" t="inlineStr">
         <is>
-          <t>Эмаль "Простокрашено!" для пола золотисто-коричневая БАУЦЕНТР 0.8 кг</t>
+          <t>Эмаль Расцвет для бетонных полов серая 2.7 кг</t>
         </is>
       </c>
       <c r="G284" s="32" t="n">
-        <v>81337</v>
+        <v>70692</v>
       </c>
       <c r="H284" s="21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -11780,7 +11772,7 @@
       </c>
       <c r="D285" s="32" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E285" s="32" t="inlineStr">
@@ -11790,11 +11782,11 @@
       </c>
       <c r="F285" s="32" t="inlineStr">
         <is>
-          <t>Эмаль "Простокрашено!" для пола золотисто-коричневая БАУЦЕНТР 1.8 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая жёлто-коричневая 0.9 кг</t>
         </is>
       </c>
       <c r="G285" s="32" t="n">
-        <v>85192</v>
+        <v>66018</v>
       </c>
       <c r="H285" s="21" t="inlineStr">
         <is>
@@ -11818,7 +11810,7 @@
       </c>
       <c r="D286" s="32" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E286" s="32" t="inlineStr">
@@ -11828,11 +11820,11 @@
       </c>
       <c r="F286" s="32" t="inlineStr">
         <is>
-          <t>Эмаль "Простокрашено!" для пола золотисто-коричневая БАУЦЕНТР 2.7 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая жёлто-коричневая 1.9 кг</t>
         </is>
       </c>
       <c r="G286" s="32" t="n">
-        <v>7652</v>
+        <v>66019</v>
       </c>
       <c r="H286" s="21" t="inlineStr">
         <is>
@@ -11866,15 +11858,15 @@
       </c>
       <c r="F287" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для бетонных полов серая 2.7 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая жёлто-коричневая 2.7 кг</t>
         </is>
       </c>
       <c r="G287" s="32" t="n">
-        <v>70692</v>
+        <v>66020</v>
       </c>
       <c r="H287" s="21" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -11904,11 +11896,11 @@
       </c>
       <c r="F288" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая жёлто-коричневая 0.9 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая золотистая 0.9 кг</t>
         </is>
       </c>
       <c r="G288" s="32" t="n">
-        <v>66018</v>
+        <v>71992</v>
       </c>
       <c r="H288" s="21" t="inlineStr">
         <is>
@@ -11942,11 +11934,11 @@
       </c>
       <c r="F289" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая жёлто-коричневая 1.9 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая золотистая 1.9 кг</t>
         </is>
       </c>
       <c r="G289" s="32" t="n">
-        <v>66019</v>
+        <v>71993</v>
       </c>
       <c r="H289" s="21" t="inlineStr">
         <is>
@@ -11980,11 +11972,11 @@
       </c>
       <c r="F290" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая жёлто-коричневая 2.7 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая золотистая 2.7 кг</t>
         </is>
       </c>
       <c r="G290" s="32" t="n">
-        <v>66020</v>
+        <v>71994</v>
       </c>
       <c r="H290" s="21" t="inlineStr">
         <is>
@@ -12018,11 +12010,11 @@
       </c>
       <c r="F291" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая золотистая 0.9 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая золотисто-коричневая 0.9 кг</t>
         </is>
       </c>
       <c r="G291" s="32" t="n">
-        <v>71992</v>
+        <v>66021</v>
       </c>
       <c r="H291" s="21" t="inlineStr">
         <is>
@@ -12056,11 +12048,11 @@
       </c>
       <c r="F292" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая золотистая 1.9 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая золотисто-коричневая 1.9 кг</t>
         </is>
       </c>
       <c r="G292" s="32" t="n">
-        <v>71993</v>
+        <v>66022</v>
       </c>
       <c r="H292" s="21" t="inlineStr">
         <is>
@@ -12094,11 +12086,11 @@
       </c>
       <c r="F293" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая золотистая 2.7 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая золотисто-коричневая 2.7 кг</t>
         </is>
       </c>
       <c r="G293" s="32" t="n">
-        <v>71994</v>
+        <v>66023</v>
       </c>
       <c r="H293" s="21" t="inlineStr">
         <is>
@@ -12132,11 +12124,11 @@
       </c>
       <c r="F294" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая золотисто-коричневая 0.9 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая красно-коричневая 0.9 кг</t>
         </is>
       </c>
       <c r="G294" s="32" t="n">
-        <v>66021</v>
+        <v>66024</v>
       </c>
       <c r="H294" s="21" t="inlineStr">
         <is>
@@ -12170,11 +12162,11 @@
       </c>
       <c r="F295" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая золотисто-коричневая 1.9 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая красно-коричневая 1.9 кг</t>
         </is>
       </c>
       <c r="G295" s="32" t="n">
-        <v>66022</v>
+        <v>66025</v>
       </c>
       <c r="H295" s="21" t="inlineStr">
         <is>
@@ -12208,11 +12200,11 @@
       </c>
       <c r="F296" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая золотисто-коричневая 2.7 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая красно-коричневая 2.7 кг</t>
         </is>
       </c>
       <c r="G296" s="32" t="n">
-        <v>66023</v>
+        <v>66026</v>
       </c>
       <c r="H296" s="21" t="inlineStr">
         <is>
@@ -12246,15 +12238,15 @@
       </c>
       <c r="F297" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая красно-коричневая 0.9 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая серая 0.9 кг</t>
         </is>
       </c>
       <c r="G297" s="32" t="n">
-        <v>66024</v>
+        <v>66379</v>
       </c>
       <c r="H297" s="21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -12284,11 +12276,11 @@
       </c>
       <c r="F298" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая красно-коричневая 1.9 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая серая 1.9 кг</t>
         </is>
       </c>
       <c r="G298" s="32" t="n">
-        <v>66025</v>
+        <v>66382</v>
       </c>
       <c r="H298" s="21" t="inlineStr">
         <is>
@@ -12322,11 +12314,11 @@
       </c>
       <c r="F299" s="32" t="inlineStr">
         <is>
-          <t>Эмаль Расцвет для пола быстросохнущая красно-коричневая 2.7 кг</t>
+          <t>Эмаль Расцвет для пола быстросохнущая серая 2.7 кг</t>
         </is>
       </c>
       <c r="G299" s="32" t="n">
-        <v>66026</v>
+        <v>66385</v>
       </c>
       <c r="H299" s="21" t="inlineStr">
         <is>
@@ -12335,88 +12327,88 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="21" t="n">
+      <c r="A300" s="23" t="n">
         <v>297</v>
       </c>
-      <c r="B300" s="32" t="inlineStr">
-        <is>
-          <t>Пол</t>
-        </is>
-      </c>
-      <c r="C300" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D300" s="32" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E300" s="32" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные для пола</t>
-        </is>
-      </c>
-      <c r="F300" s="32" t="inlineStr">
-        <is>
-          <t>Эмаль Расцвет для пола быстросохнущая серая 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G300" s="32" t="n">
-        <v>66379</v>
-      </c>
-      <c r="H300" s="21" t="inlineStr">
-        <is>
-          <t>В</t>
+      <c r="B300" s="33" t="inlineStr">
+        <is>
+          <t>Фасад</t>
+        </is>
+      </c>
+      <c r="C300" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D300" s="33" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E300" s="33" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F300" s="33" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE MODERN PRO» фасадная водно-дисперсионная силиконовая матовая (База А)</t>
+        </is>
+      </c>
+      <c r="G300" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" s="23" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="21" t="n">
+      <c r="A301" s="23" t="n">
         <v>298</v>
       </c>
-      <c r="B301" s="32" t="inlineStr">
-        <is>
-          <t>Пол</t>
-        </is>
-      </c>
-      <c r="C301" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D301" s="32" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E301" s="32" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные для пола</t>
-        </is>
-      </c>
-      <c r="F301" s="32" t="inlineStr">
-        <is>
-          <t>Эмаль Расцвет для пола быстросохнущая серая 1.9 кг</t>
-        </is>
-      </c>
-      <c r="G301" s="32" t="n">
-        <v>66382</v>
-      </c>
-      <c r="H301" s="21" t="inlineStr">
-        <is>
-          <t>А</t>
+      <c r="B301" s="33" t="inlineStr">
+        <is>
+          <t>Фасад</t>
+        </is>
+      </c>
+      <c r="C301" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D301" s="33" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E301" s="33" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F301" s="33" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE MODERN PRO» фасадная водно-дисперсионная силиконовая матовая (База С)</t>
+        </is>
+      </c>
+      <c r="G301" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H301" s="23" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="21" t="n">
+      <c r="A302" s="23" t="n">
         <v>299</v>
       </c>
-      <c r="B302" s="32" t="inlineStr">
-        <is>
-          <t>Пол</t>
+      <c r="B302" s="33" t="inlineStr">
+        <is>
+          <t>Фасад</t>
         </is>
       </c>
       <c r="C302" s="29" t="inlineStr">
@@ -12424,27 +12416,27 @@
           <t>Органическая</t>
         </is>
       </c>
-      <c r="D302" s="32" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E302" s="32" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные для пола</t>
-        </is>
-      </c>
-      <c r="F302" s="32" t="inlineStr">
-        <is>
-          <t>Эмаль Расцвет для пола быстросохнущая серая 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G302" s="32" t="n">
-        <v>66385</v>
-      </c>
-      <c r="H302" s="21" t="inlineStr">
-        <is>
-          <t>А</t>
+      <c r="D302" s="33" t="inlineStr">
+        <is>
+          <t>AvantGarde</t>
+        </is>
+      </c>
+      <c r="E302" s="33" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F302" s="33" t="inlineStr">
+        <is>
+          <t>Краска фасадная AvantGarde (база А) белая</t>
+        </is>
+      </c>
+      <c r="G302" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" s="23" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -12464,7 +12456,7 @@
       </c>
       <c r="D303" s="33" t="inlineStr">
         <is>
-          <t>СТРОЙКОМПЛЕКТ</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E303" s="33" t="inlineStr">
@@ -12474,15 +12466,15 @@
       </c>
       <c r="F303" s="33" t="inlineStr">
         <is>
-          <t>Краска фасадная СТРОЙКОМПЛЕКТ 13 кг</t>
+          <t>Краска фасадная AvantGarde (база С)</t>
         </is>
       </c>
       <c r="G303" s="33" t="n">
-        <v>73122</v>
+        <v>0</v>
       </c>
       <c r="H303" s="23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -12557,22 +12549,22 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>6</v>
       </c>
       <c r="F4" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмали 3-в-1, эмали по металлу и ржавчине — заборы, ворота, трубы, гаражи</t>
+          <t>Грунт-эмали 3-в-1, эмали по металлу — заборы, ворота, трубы, гаражи</t>
         </is>
       </c>
     </row>
@@ -12583,22 +12575,22 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F5" s="30" t="inlineStr">
         <is>
-          <t>Краски интерьерные, моющиеся, потолочные, шпатлёвки, грунтовки — стены, потолки</t>
+          <t>Краски интерьерные, шпатлёвки, грунтовки — стены, потолки</t>
         </is>
       </c>
     </row>
@@ -12609,22 +12601,22 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="D6" s="19" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="31" t="inlineStr">
         <is>
-          <t>Лаки, пропитки, антисептики, декоративные составы — окна, двери, террасы</t>
+          <t>Лаки, пропитки, антисептики, защитно-декоративные — окна, двери, террасы</t>
         </is>
       </c>
     </row>
@@ -12661,22 +12653,22 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="33" t="inlineStr">
         <is>
-          <t>Краски фасадные, грунтовки фасадные — наружные стены зданий</t>
+          <t>Краски фасадные ВД — наружные стены зданий (NEWTONE, AvantGarde)</t>
         </is>
       </c>
     </row>
@@ -12695,10 +12687,10 @@
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F9" s="34" t="n"/>
     </row>

--- a/download/Ассортимент_Олимп_300_SKU.xlsx
+++ b/download/Ассортимент_Олимп_300_SKU.xlsx
@@ -580,10 +580,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -601,14 +601,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Стартовый ассортимент Олимп — 300 SKU (сбалансированный)</t>
+          <t>Стартовый ассортимент Олимп — 300 SKU (сбалансированный + новинки)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABC-анализ + прайс-лист · Убраны: СТРОЙКОМПЛЕКТ, EMPILS ЭКОНОМ, NoName · Добавлены: NEWTONE (14), AvantGarde (17)</t>
+          <t>ABC + прайс + новинки 2026 · Убраны: СТРОЙКОМПЛЕКТ, EMPILS ЭКОНОМ, NoName · Добавлены: NEWTONE, AvantGarde, 8 новинок</t>
         </is>
       </c>
     </row>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>19</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>23</v>
@@ -683,11 +683,11 @@
         <v>2</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>72.3%</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>5</v>
@@ -713,11 +713,11 @@
         <v>2</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>27.7%</t>
         </is>
       </c>
     </row>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>34</v>
@@ -829,14 +829,14 @@
         <v>6</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H12" s="14" t="n">
         <v>46</v>
       </c>
       <c r="I12" s="15" t="inlineStr"/>
       <c r="J12" s="7" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -847,13 +847,13 @@
       </c>
       <c r="B13" s="15" t="inlineStr"/>
       <c r="C13" s="17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" s="17" t="n">
         <v>29</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>2</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="I13" s="15" t="inlineStr"/>
       <c r="J13" s="7" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14">
@@ -887,10 +887,10 @@
       </c>
       <c r="H14" s="15" t="inlineStr"/>
       <c r="I14" s="19" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -949,25 +949,25 @@
         <v>15</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>29</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>17</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>54</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J17" s="24" t="n">
         <v>300</v>
@@ -976,28 +976,63 @@
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>ABC-АНАЛИЗ 300 SKU:</t>
+          <t>НОВИНКИ 2026 (8 SKU — топ цвета и фасовки):</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>Группа А: 123 SKU (41%) — топ-продавцы</t>
+          <t xml:space="preserve">  • PROFIWOOD скандинавский серый 0.8 л (топ-1 цвет, топ-1 фасовка)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>Группа В: 76 SKU (25%) — средние</t>
+          <t xml:space="preserve">  • PROFIWOOD скандинавский серый 2.4 л (топ-1 цвет, топ-2 фасовка)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>Группа С: 101 SKU (34%) — хвост + новинки</t>
+          <t xml:space="preserve">  • PROFIWOOD бежевый 0.8 л (топ-2 цвет, топ-1 фасовка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • PROFIWOOD бежевый 2.4 л (топ-2 цвет, топ-2 фасовка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Ореол краска для плит OSB 6 кг (бестселлер — 4 344 кг)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • NEWTONE ABSOLUTE BLACK 10 л (бестселлер — 598 кг)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • NEWTONE SKY потолочная 9 л (бестселлер — 188 кг)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Ореол резиновая ВД 3 кг (бестселлер — 1 908 кг)</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1067,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Стартовый ассортимент 300 SKU для Олимп (сбалансированный)</t>
+          <t>Стартовый ассортимент 300 SKU для Олимп (сбалансированный + новинки)</t>
         </is>
       </c>
     </row>
@@ -3954,15 +3989,15 @@
       </c>
       <c r="F79" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 белая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 1.9 кг</t>
         </is>
       </c>
       <c r="G79" s="27" t="n">
-        <v>65174</v>
+        <v>65199</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -3992,11 +4027,11 @@
       </c>
       <c r="F80" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 голубая 0.9 кг</t>
         </is>
       </c>
       <c r="G80" s="27" t="n">
-        <v>65198</v>
+        <v>65189</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -4030,15 +4065,15 @@
       </c>
       <c r="F81" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 0.9 кг</t>
         </is>
       </c>
       <c r="G81" s="27" t="n">
-        <v>65199</v>
+        <v>65204</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4068,15 +4103,15 @@
       </c>
       <c r="F82" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 вишневая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 1.9 кг</t>
         </is>
       </c>
       <c r="G82" s="27" t="n">
-        <v>65200</v>
+        <v>65205</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4106,15 +4141,15 @@
       </c>
       <c r="F83" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 голубая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 0.9 кг</t>
         </is>
       </c>
       <c r="G83" s="27" t="n">
-        <v>65189</v>
+        <v>65192</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4144,15 +4179,15 @@
       </c>
       <c r="F84" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 1.9 кг</t>
         </is>
       </c>
       <c r="G84" s="27" t="n">
-        <v>65204</v>
+        <v>65193</v>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4182,15 +4217,15 @@
       </c>
       <c r="F85" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 2.7 кг</t>
         </is>
       </c>
       <c r="G85" s="27" t="n">
-        <v>65205</v>
+        <v>65194</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4220,15 +4255,15 @@
       </c>
       <c r="F86" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 желтая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 0.9 кг</t>
         </is>
       </c>
       <c r="G86" s="27" t="n">
-        <v>65206</v>
+        <v>72966</v>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4258,11 +4293,11 @@
       </c>
       <c r="F87" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 1.9 кг</t>
         </is>
       </c>
       <c r="G87" s="27" t="n">
-        <v>65192</v>
+        <v>72968</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
@@ -4296,15 +4331,15 @@
       </c>
       <c r="F88" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 2.7 кг</t>
         </is>
       </c>
       <c r="G88" s="27" t="n">
-        <v>65193</v>
+        <v>72971</v>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4334,15 +4369,15 @@
       </c>
       <c r="F89" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 зеленая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 0.9 кг</t>
         </is>
       </c>
       <c r="G89" s="27" t="n">
-        <v>65194</v>
+        <v>65176</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4372,15 +4407,15 @@
       </c>
       <c r="F90" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 1.9 кг</t>
         </is>
       </c>
       <c r="G90" s="27" t="n">
-        <v>72966</v>
+        <v>65177</v>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4410,15 +4445,15 @@
       </c>
       <c r="F91" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 2.7 кг</t>
         </is>
       </c>
       <c r="G91" s="27" t="n">
-        <v>72968</v>
+        <v>65178</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4448,15 +4483,15 @@
       </c>
       <c r="F92" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 светло-серая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 5 кг</t>
         </is>
       </c>
       <c r="G92" s="27" t="n">
-        <v>72971</v>
+        <v>70246</v>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4486,15 +4521,15 @@
       </c>
       <c r="F93" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 0.9 кг</t>
         </is>
       </c>
       <c r="G93" s="27" t="n">
-        <v>65176</v>
+        <v>87388</v>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4524,11 +4559,11 @@
       </c>
       <c r="F94" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 1.9 кг</t>
         </is>
       </c>
       <c r="G94" s="27" t="n">
-        <v>65177</v>
+        <v>87389</v>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
@@ -4562,15 +4597,15 @@
       </c>
       <c r="F95" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 0.9 кг</t>
         </is>
       </c>
       <c r="G95" s="27" t="n">
-        <v>65178</v>
+        <v>65201</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4600,15 +4635,15 @@
       </c>
       <c r="F96" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серая 5 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 1.9 кг</t>
         </is>
       </c>
       <c r="G96" s="27" t="n">
-        <v>70246</v>
+        <v>65202</v>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4638,15 +4673,15 @@
       </c>
       <c r="F97" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 2.7 кг</t>
         </is>
       </c>
       <c r="G97" s="27" t="n">
-        <v>87388</v>
+        <v>65203</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4676,15 +4711,15 @@
       </c>
       <c r="F98" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 тёмно-зелёная 0.9 кг</t>
         </is>
       </c>
       <c r="G98" s="27" t="n">
-        <v>87389</v>
+        <v>72960</v>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -4714,15 +4749,15 @@
       </c>
       <c r="F99" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 серый графит RAL 7024 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 0.9 кг</t>
         </is>
       </c>
       <c r="G99" s="27" t="n">
-        <v>87390</v>
+        <v>65186</v>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4752,15 +4787,15 @@
       </c>
       <c r="F100" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 1.9 кг</t>
         </is>
       </c>
       <c r="G100" s="27" t="n">
-        <v>65201</v>
+        <v>65187</v>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4790,15 +4825,15 @@
       </c>
       <c r="F101" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 2.7 кг</t>
         </is>
       </c>
       <c r="G101" s="27" t="n">
-        <v>65202</v>
+        <v>65188</v>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4828,15 +4863,15 @@
       </c>
       <c r="F102" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 синяя 2.7 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 5 кг</t>
         </is>
       </c>
       <c r="G102" s="27" t="n">
-        <v>65203</v>
+        <v>70253</v>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4866,15 +4901,15 @@
       </c>
       <c r="F103" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 тёмно-зелёная 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 0.9 кг</t>
         </is>
       </c>
       <c r="G103" s="27" t="n">
-        <v>72960</v>
+        <v>65195</v>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -4904,11 +4939,11 @@
       </c>
       <c r="F104" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 0.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 1.9 кг</t>
         </is>
       </c>
       <c r="G104" s="27" t="n">
-        <v>65186</v>
+        <v>65196</v>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
@@ -4942,15 +4977,15 @@
       </c>
       <c r="F105" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 1.9 кг</t>
+          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 2.7 кг</t>
         </is>
       </c>
       <c r="G105" s="27" t="n">
-        <v>65187</v>
+        <v>65197</v>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -4980,11 +5015,11 @@
       </c>
       <c r="F106" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 2.7 кг</t>
+          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая черная 0.9 кг</t>
         </is>
       </c>
       <c r="G106" s="27" t="n">
-        <v>65188</v>
+        <v>82708</v>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
@@ -5018,11 +5053,11 @@
       </c>
       <c r="F107" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 черная 5 кг</t>
+          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая черная 2.7 кг</t>
         </is>
       </c>
       <c r="G107" s="27" t="n">
-        <v>70253</v>
+        <v>82709</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -5051,20 +5086,20 @@
       </c>
       <c r="E108" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F108" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 0.9 кг</t>
+          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G108" s="27" t="n">
-        <v>65195</v>
+        <v>9039</v>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5089,20 +5124,20 @@
       </c>
       <c r="E109" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F109" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 1.9 кг</t>
+          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G109" s="27" t="n">
-        <v>65196</v>
+        <v>9040</v>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5127,20 +5162,20 @@
       </c>
       <c r="E110" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F110" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль "РАСЦВЕТ" 3 в 1 шоколадная 2.7 кг</t>
+          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G110" s="27" t="n">
-        <v>65197</v>
+        <v>9041</v>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -5165,16 +5200,16 @@
       </c>
       <c r="E111" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F111" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая серая 0.9 кг</t>
+          <t>Эмаль ПФ-115 голубая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G111" s="27" t="n">
-        <v>82704</v>
+        <v>9090</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
@@ -5203,16 +5238,16 @@
       </c>
       <c r="E112" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F112" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая черная 0.9 кг</t>
+          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G112" s="27" t="n">
-        <v>82708</v>
+        <v>9213</v>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
@@ -5241,16 +5276,16 @@
       </c>
       <c r="E113" s="27" t="inlineStr">
         <is>
-          <t>Грунт-Эмаль</t>
+          <t>Эмали Алкидные</t>
         </is>
       </c>
       <c r="F113" s="27" t="inlineStr">
         <is>
-          <t>Грунт-эмаль быстросохнущая "РАСЦВЕТ" матовая черная 2.7 кг</t>
+          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G113" s="27" t="n">
-        <v>82709</v>
+        <v>9214</v>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
@@ -5284,15 +5319,15 @@
       </c>
       <c r="F114" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 0.9 кг</t>
+          <t>Эмаль ПФ-115 коричневая РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G114" s="27" t="n">
-        <v>9039</v>
+        <v>9232</v>
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5322,15 +5357,15 @@
       </c>
       <c r="F115" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 1.9 кг</t>
+          <t>Эмаль ПФ-115 коричневая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G115" s="27" t="n">
-        <v>9040</v>
+        <v>9234</v>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5360,15 +5395,15 @@
       </c>
       <c r="F116" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 белая РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль ПФ-115 красная РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G116" s="27" t="n">
-        <v>9041</v>
+        <v>9258</v>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5398,11 +5433,11 @@
       </c>
       <c r="F117" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 вишнёвая РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль ПФ-115 красная РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G117" s="27" t="n">
-        <v>9064</v>
+        <v>9260</v>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
@@ -5436,15 +5471,15 @@
       </c>
       <c r="F118" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 голубая РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G118" s="27" t="n">
-        <v>9090</v>
+        <v>9749</v>
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5474,15 +5509,15 @@
       </c>
       <c r="F119" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 0.9 кг</t>
+          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G119" s="27" t="n">
-        <v>9212</v>
+        <v>9750</v>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -5512,11 +5547,11 @@
       </c>
       <c r="F120" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 1.9 кг</t>
+          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G120" s="27" t="n">
-        <v>9213</v>
+        <v>9751</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
@@ -5550,15 +5585,15 @@
       </c>
       <c r="F121" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 зелёная РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль ПФ-115 синяя РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G121" s="27" t="n">
-        <v>9214</v>
+        <v>9781</v>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5588,15 +5623,15 @@
       </c>
       <c r="F122" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 коричневая РАСЦВЕТ ГОСТ 0.9 кг</t>
+          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G122" s="27" t="n">
-        <v>9232</v>
+        <v>10093</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5626,15 +5661,15 @@
       </c>
       <c r="F123" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 коричневая РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G123" s="27" t="n">
-        <v>9234</v>
+        <v>10094</v>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5664,11 +5699,11 @@
       </c>
       <c r="F124" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 красная РАСЦВЕТ ГОСТ 0.9 кг</t>
+          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G124" s="27" t="n">
-        <v>9258</v>
+        <v>10095</v>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
@@ -5702,15 +5737,15 @@
       </c>
       <c r="F125" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 красная РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G125" s="27" t="n">
-        <v>9260</v>
+        <v>10102</v>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -5740,11 +5775,11 @@
       </c>
       <c r="F126" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 0.9 кг</t>
+          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 1.9 кг</t>
         </is>
       </c>
       <c r="G126" s="27" t="n">
-        <v>9749</v>
+        <v>10103</v>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
@@ -5778,15 +5813,15 @@
       </c>
       <c r="F127" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 1.9 кг</t>
+          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G127" s="27" t="n">
-        <v>9750</v>
+        <v>10104</v>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -5816,11 +5851,11 @@
       </c>
       <c r="F128" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 серая РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль ПФ-115 ярко-жёлтая РАСЦВЕТ ГОСТ 0.9 кг</t>
         </is>
       </c>
       <c r="G128" s="27" t="n">
-        <v>9751</v>
+        <v>10179</v>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
@@ -5854,11 +5889,11 @@
       </c>
       <c r="F129" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 синяя РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль ПФ-115 ярко-жёлтая РАСЦВЕТ ГОСТ 2.7 кг</t>
         </is>
       </c>
       <c r="G129" s="27" t="n">
-        <v>9781</v>
+        <v>10181</v>
       </c>
       <c r="H129" s="14" t="inlineStr">
         <is>
@@ -5892,15 +5927,15 @@
       </c>
       <c r="F130" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 0.9 кг</t>
+          <t>Эмаль с молотковым эффектом РАСЦВЕТ коричневая 0.8 кг</t>
         </is>
       </c>
       <c r="G130" s="27" t="n">
-        <v>10093</v>
+        <v>77633</v>
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5930,15 +5965,15 @@
       </c>
       <c r="F131" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 1.9 кг</t>
+          <t>Эмаль с молотковым эффектом РАСЦВЕТ чёрная 0.8 кг</t>
         </is>
       </c>
       <c r="G131" s="27" t="n">
-        <v>10094</v>
+        <v>77618</v>
       </c>
       <c r="H131" s="14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -5968,11 +6003,11 @@
       </c>
       <c r="F132" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 чёрная РАСЦВЕТ ГОСТ 2.7 кг</t>
+          <t>Эмаль универсальная ПФ-115 Расцвет белая матовая 0.9 кг</t>
         </is>
       </c>
       <c r="G132" s="27" t="n">
-        <v>10095</v>
+        <v>10816</v>
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
@@ -6006,317 +6041,317 @@
       </c>
       <c r="F133" s="27" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 0.9 кг</t>
+          <t>Эмаль универсальная ПФ-115 Расцвет белая матовая 2.7 кг</t>
         </is>
       </c>
       <c r="G133" s="27" t="n">
-        <v>10102</v>
+        <v>10818</v>
       </c>
       <c r="H133" s="14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="14" t="n">
+      <c r="A134" s="17" t="n">
         <v>131</v>
       </c>
-      <c r="B134" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C134" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D134" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E134" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F134" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 1.9 кг</t>
-        </is>
-      </c>
-      <c r="G134" s="27" t="n">
-        <v>10103</v>
-      </c>
-      <c r="H134" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
+      <c r="B134" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C134" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D134" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E134" s="30" t="inlineStr">
+        <is>
+          <t>Грунтовки</t>
+        </is>
+      </c>
+      <c r="F134" s="30" t="inlineStr">
+        <is>
+          <t>Грунтовка глубокого проникновения с антисептиком «NEWTONE» водно-дисперсионная полиакриловая для наружных и внутренних работ</t>
+        </is>
+      </c>
+      <c r="G134" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="14" t="n">
+      <c r="A135" s="17" t="n">
         <v>132</v>
       </c>
-      <c r="B135" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C135" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D135" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E135" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F135" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 шоколадная РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G135" s="27" t="n">
-        <v>10104</v>
-      </c>
-      <c r="H135" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
+      <c r="B135" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C135" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D135" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E135" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F135" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE INTERIO» суперстойкая интерьерная водно-дисперсионная латексная матовая (База C)</t>
+        </is>
+      </c>
+      <c r="G135" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="14" t="n">
+      <c r="A136" s="17" t="n">
         <v>133</v>
       </c>
-      <c r="B136" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C136" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D136" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E136" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F136" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 ярко-жёлтая РАСЦВЕТ ГОСТ 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G136" s="27" t="n">
-        <v>10179</v>
-      </c>
-      <c r="H136" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
+      <c r="B136" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C136" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D136" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E136" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F136" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE INTERIO» суперстойкая интерьерная водно-дисперсионная латексная матовая (База А)</t>
+        </is>
+      </c>
+      <c r="G136" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="14" t="n">
+      <c r="A137" s="17" t="n">
         <v>134</v>
       </c>
-      <c r="B137" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C137" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D137" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E137" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F137" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 ярко-жёлтая РАСЦВЕТ ГОСТ 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G137" s="27" t="n">
-        <v>10181</v>
-      </c>
-      <c r="H137" s="14" t="inlineStr">
+      <c r="B137" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C137" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D137" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E137" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F137" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 20» моющаяся интерьерная водно-дисперсионная латексная полуматовая (База A)</t>
+        </is>
+      </c>
+      <c r="G137" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="17" t="inlineStr">
         <is>
           <t>С</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="14" t="n">
+      <c r="A138" s="17" t="n">
         <v>135</v>
       </c>
-      <c r="B138" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C138" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D138" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E138" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F138" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль с молотковым эффектом РАСЦВЕТ коричневая 0.8 кг</t>
-        </is>
-      </c>
-      <c r="G138" s="27" t="n">
-        <v>77633</v>
-      </c>
-      <c r="H138" s="14" t="inlineStr">
+      <c r="B138" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C138" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D138" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E138" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F138" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 20» моющаяся интерьерная водно-дисперсионная латексная полуматовая (База C)</t>
+        </is>
+      </c>
+      <c r="G138" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="17" t="inlineStr">
         <is>
           <t>С</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="14" t="n">
+      <c r="A139" s="17" t="n">
         <v>136</v>
       </c>
-      <c r="B139" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C139" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D139" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E139" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F139" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль с молотковым эффектом РАСЦВЕТ чёрная 0.8 кг</t>
-        </is>
-      </c>
-      <c r="G139" s="27" t="n">
-        <v>77618</v>
-      </c>
-      <c r="H139" s="14" t="inlineStr">
+      <c r="B139" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C139" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D139" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E139" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F139" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 3» моющаяся интерьерная водно-дисперсионная латексная глубокоматовая (База C)</t>
+        </is>
+      </c>
+      <c r="G139" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="17" t="inlineStr">
         <is>
           <t>С</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="14" t="n">
+      <c r="A140" s="17" t="n">
         <v>137</v>
       </c>
-      <c r="B140" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C140" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D140" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E140" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F140" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль универсальная ПФ-115 Расцвет белая матовая 0.9 кг</t>
-        </is>
-      </c>
-      <c r="G140" s="27" t="n">
-        <v>10816</v>
-      </c>
-      <c r="H140" s="14" t="inlineStr">
-        <is>
-          <t>В</t>
+      <c r="B140" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C140" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D140" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E140" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F140" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 3» моющаяся интерьерная водно-дисперсионная латексная глубокоматовая (База А)</t>
+        </is>
+      </c>
+      <c r="G140" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="17" t="inlineStr">
+        <is>
+          <t>С</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="14" t="n">
+      <c r="A141" s="17" t="n">
         <v>138</v>
       </c>
-      <c r="B141" s="27" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="C141" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D141" s="27" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E141" s="27" t="inlineStr">
-        <is>
-          <t>Эмали Алкидные</t>
-        </is>
-      </c>
-      <c r="F141" s="27" t="inlineStr">
-        <is>
-          <t>Эмаль универсальная ПФ-115 Расцвет белая матовая 2.7 кг</t>
-        </is>
-      </c>
-      <c r="G141" s="27" t="n">
-        <v>10818</v>
-      </c>
-      <c r="H141" s="14" t="inlineStr">
+      <c r="B141" s="30" t="inlineStr">
+        <is>
+          <t>Помещения (интерьер)</t>
+        </is>
+      </c>
+      <c r="C141" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D141" s="30" t="inlineStr">
+        <is>
+          <t>NEWTONE</t>
+        </is>
+      </c>
+      <c r="E141" s="30" t="inlineStr">
+        <is>
+          <t>Краски</t>
+        </is>
+      </c>
+      <c r="F141" s="30" t="inlineStr">
+        <is>
+          <t>Краска «NEWTONE LOTUS 7» моющаяся интерьерная водно-дисперсионная латексная матовая (База C)</t>
+        </is>
+      </c>
+      <c r="G141" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="17" t="inlineStr">
         <is>
           <t>С</t>
         </is>
@@ -6343,12 +6378,12 @@
       </c>
       <c r="E142" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F142" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка глубокого проникновения с антисептиком «NEWTONE» водно-дисперсионная полиакриловая для наружных и внутренних работ</t>
+          <t>Краска «NEWTONE LOTUS 7» моющаяся интерьерная водно-дисперсионная латексная матовая (База А)</t>
         </is>
       </c>
       <c r="G142" s="30" t="n">
@@ -6386,15 +6421,15 @@
       </c>
       <c r="F143" s="30" t="inlineStr">
         <is>
-          <t>Краска «NEWTONE INTERIO» суперстойкая интерьерная водно-дисперсионная латексная матовая (База C)</t>
+          <t>Краска ВД «NEWTONE ABSOLUTE BLACK» для интерьеров моющаяся глубокоматовая черная RAL 9005 10 л 13.9 кг</t>
         </is>
       </c>
       <c r="G143" s="30" t="n">
-        <v>0</v>
+        <v>89508</v>
       </c>
       <c r="H143" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -6424,15 +6459,15 @@
       </c>
       <c r="F144" s="30" t="inlineStr">
         <is>
-          <t>Краска «NEWTONE INTERIO» суперстойкая интерьерная водно-дисперсионная латексная матовая (База А)</t>
+          <t>Краска ВД «NEWTONE SKY» для потолков ультрабелая 9 л 14.5 кг</t>
         </is>
       </c>
       <c r="G144" s="30" t="n">
-        <v>0</v>
+        <v>89357</v>
       </c>
       <c r="H144" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6497,7 @@
       </c>
       <c r="F145" s="30" t="inlineStr">
         <is>
-          <t>Краска «NEWTONE LOTUS 20» моющаяся интерьерная водно-дисперсионная латексная полуматовая (База A)</t>
+          <t>Краска ВД «NEWTONE SKY» для потолков ультрабелая водно-дисперсионная латексная</t>
         </is>
       </c>
       <c r="G145" s="30" t="n">
@@ -6500,7 +6535,7 @@
       </c>
       <c r="F146" s="30" t="inlineStr">
         <is>
-          <t>Краска «NEWTONE LOTUS 20» моющаяся интерьерная водно-дисперсионная латексная полуматовая (База C)</t>
+          <t>Краска для интерьеров моющаяся глубокоматовая «NEWTONE» водно-дисперсионная полиакриловая для внутренних работ черная RAL 9005</t>
         </is>
       </c>
       <c r="G146" s="30" t="n">
@@ -6533,12 +6568,12 @@
       </c>
       <c r="E147" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F147" s="30" t="inlineStr">
         <is>
-          <t>Краска «NEWTONE LOTUS 3» моющаяся интерьерная водно-дисперсионная латексная глубокоматовая (База C)</t>
+          <t>Шпатлевка супер финишная «NEWTONE» водно-дисперсионная полиакриловая для внутренних работ</t>
         </is>
       </c>
       <c r="G147" s="30" t="n">
@@ -6566,7 +6601,7 @@
       </c>
       <c r="D148" s="30" t="inlineStr">
         <is>
-          <t>NEWTONE</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E148" s="30" t="inlineStr">
@@ -6576,15 +6611,15 @@
       </c>
       <c r="F148" s="30" t="inlineStr">
         <is>
-          <t>Краска «NEWTONE LOTUS 3» моющаяся интерьерная водно-дисперсионная латексная глубокоматовая (База А)</t>
+          <t>Краска ВД Ореол белоснежная для потолков 3 кг</t>
         </is>
       </c>
       <c r="G148" s="30" t="n">
-        <v>0</v>
+        <v>5372</v>
       </c>
       <c r="H148" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6639,7 @@
       </c>
       <c r="D149" s="30" t="inlineStr">
         <is>
-          <t>NEWTONE</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E149" s="30" t="inlineStr">
@@ -6614,15 +6649,15 @@
       </c>
       <c r="F149" s="30" t="inlineStr">
         <is>
-          <t>Краска «NEWTONE LOTUS 7» моющаяся интерьерная водно-дисперсионная латексная матовая (База C)</t>
+          <t>Краска ВД Ореол белоснежная для стен и потолков 13 кг</t>
         </is>
       </c>
       <c r="G149" s="30" t="n">
-        <v>0</v>
+        <v>5385</v>
       </c>
       <c r="H149" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6677,7 @@
       </c>
       <c r="D150" s="30" t="inlineStr">
         <is>
-          <t>NEWTONE</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E150" s="30" t="inlineStr">
@@ -6652,15 +6687,15 @@
       </c>
       <c r="F150" s="30" t="inlineStr">
         <is>
-          <t>Краска «NEWTONE LOTUS 7» моющаяся интерьерная водно-дисперсионная латексная матовая (База А)</t>
+          <t>Краска ВД Ореол белоснежная для стен и потолков 3 кг</t>
         </is>
       </c>
       <c r="G150" s="30" t="n">
-        <v>0</v>
+        <v>5390</v>
       </c>
       <c r="H150" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6715,7 @@
       </c>
       <c r="D151" s="30" t="inlineStr">
         <is>
-          <t>NEWTONE</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E151" s="30" t="inlineStr">
@@ -6690,11 +6725,11 @@
       </c>
       <c r="F151" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД «NEWTONE SKY» для потолков ультрабелая водно-дисперсионная латексная</t>
+          <t>Краска ВД Ореол белоснежная для стен и потолков 6.5 кг</t>
         </is>
       </c>
       <c r="G151" s="30" t="n">
-        <v>0</v>
+        <v>5396</v>
       </c>
       <c r="H151" s="17" t="inlineStr">
         <is>
@@ -6718,7 +6753,7 @@
       </c>
       <c r="D152" s="30" t="inlineStr">
         <is>
-          <t>NEWTONE</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E152" s="30" t="inlineStr">
@@ -6728,11 +6763,11 @@
       </c>
       <c r="F152" s="30" t="inlineStr">
         <is>
-          <t>Краска для интерьеров моющаяся глубокоматовая «NEWTONE» водно-дисперсионная полиакриловая для внутренних работ черная RAL 9005</t>
+          <t>Краска ВД Ореол для стен и потолков моющаяся 3 кг</t>
         </is>
       </c>
       <c r="G152" s="30" t="n">
-        <v>0</v>
+        <v>5468</v>
       </c>
       <c r="H152" s="17" t="inlineStr">
         <is>
@@ -6756,21 +6791,21 @@
       </c>
       <c r="D153" s="30" t="inlineStr">
         <is>
-          <t>NEWTONE</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E153" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F153" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка супер финишная «NEWTONE» водно-дисперсионная полиакриловая для внутренних работ</t>
+          <t>Краска ВД Ореол для стен и потолков моющаяся 6.5 кг</t>
         </is>
       </c>
       <c r="G153" s="30" t="n">
-        <v>0</v>
+        <v>5470</v>
       </c>
       <c r="H153" s="17" t="inlineStr">
         <is>
@@ -6804,15 +6839,15 @@
       </c>
       <c r="F154" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол белоснежная для потолков 3 кг</t>
+          <t>Краска ВД резиновая Ореол (База А) 3 кг</t>
         </is>
       </c>
       <c r="G154" s="30" t="n">
-        <v>5372</v>
+        <v>89856</v>
       </c>
       <c r="H154" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -6842,11 +6877,11 @@
       </c>
       <c r="F155" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол белоснежная для стен и потолков 13 кг</t>
+          <t>Краска для плит OSB Ореол (база А) 6 кг</t>
         </is>
       </c>
       <c r="G155" s="30" t="n">
-        <v>5385</v>
+        <v>88966</v>
       </c>
       <c r="H155" s="17" t="inlineStr">
         <is>
@@ -6875,16 +6910,16 @@
       </c>
       <c r="E156" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F156" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол белоснежная для стен и потолков 3 кг</t>
+          <t>Шпатлевка Ореол фасадная влагостойкая ВД акриловая 1.5 кг</t>
         </is>
       </c>
       <c r="G156" s="30" t="n">
-        <v>5390</v>
+        <v>66128</v>
       </c>
       <c r="H156" s="17" t="inlineStr">
         <is>
@@ -6913,20 +6948,20 @@
       </c>
       <c r="E157" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F157" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол белоснежная для стен и потолков 6.5 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая белая (пластиковая тара) 0.9 кг</t>
         </is>
       </c>
       <c r="G157" s="30" t="n">
-        <v>5396</v>
+        <v>70644</v>
       </c>
       <c r="H157" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -6951,20 +6986,20 @@
       </c>
       <c r="E158" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F158" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол для стен и потолков моющаяся 3 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая белая 2.5 кг</t>
         </is>
       </c>
       <c r="G158" s="30" t="n">
-        <v>5468</v>
+        <v>85884</v>
       </c>
       <c r="H158" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -6989,20 +7024,20 @@
       </c>
       <c r="E159" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F159" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол для стен и потолков моющаяся 6.5 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая серая 0.9 кг</t>
         </is>
       </c>
       <c r="G159" s="30" t="n">
-        <v>5470</v>
+        <v>65254</v>
       </c>
       <c r="H159" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -7027,20 +7062,20 @@
       </c>
       <c r="E160" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Эмали ВДАК</t>
         </is>
       </c>
       <c r="F160" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка Ореол фасадная влагостойкая ВД акриловая 1.5 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая слоновая кость 0.9 кг</t>
         </is>
       </c>
       <c r="G160" s="30" t="n">
-        <v>66128</v>
+        <v>78181</v>
       </c>
       <c r="H160" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -7070,15 +7105,15 @@
       </c>
       <c r="F161" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая белая (пластиковая тара) 0.9 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" глянцевая черная 0.9 кг</t>
         </is>
       </c>
       <c r="G161" s="30" t="n">
-        <v>70644</v>
+        <v>65252</v>
       </c>
       <c r="H161" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -7108,11 +7143,11 @@
       </c>
       <c r="F162" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая белая 2.5 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" матовая белая (пластиковая тара) 0.9 кг</t>
         </is>
       </c>
       <c r="G162" s="30" t="n">
-        <v>85884</v>
+        <v>70661</v>
       </c>
       <c r="H162" s="17" t="inlineStr">
         <is>
@@ -7146,15 +7181,15 @@
       </c>
       <c r="F163" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая серая 0.9 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" матовая белая (пластиковая тара) 2.5 кг</t>
         </is>
       </c>
       <c r="G163" s="30" t="n">
-        <v>65254</v>
+        <v>70662</v>
       </c>
       <c r="H163" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7184,11 +7219,11 @@
       </c>
       <c r="F164" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая слоновая кость 0.9 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" матовая серая 0.9 кг</t>
         </is>
       </c>
       <c r="G164" s="30" t="n">
-        <v>78181</v>
+        <v>71787</v>
       </c>
       <c r="H164" s="17" t="inlineStr">
         <is>
@@ -7222,15 +7257,15 @@
       </c>
       <c r="F165" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" глянцевая черная 0.9 кг</t>
+          <t>Эмаль акриловая "ОРЕОЛ" матовая чёрная 0.9 кг</t>
         </is>
       </c>
       <c r="G165" s="30" t="n">
-        <v>65252</v>
+        <v>71790</v>
       </c>
       <c r="H165" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -7250,21 +7285,21 @@
       </c>
       <c r="D166" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E166" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F166" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" матовая белая (пластиковая тара) 0.9 кг</t>
+          <t>Грунт-концентрат ВД-ВА Ореол Дисконт 1 кг</t>
         </is>
       </c>
       <c r="G166" s="30" t="n">
-        <v>70661</v>
+        <v>4209</v>
       </c>
       <c r="H166" s="17" t="inlineStr">
         <is>
@@ -7288,25 +7323,25 @@
       </c>
       <c r="D167" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E167" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F167" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" матовая белая (пластиковая тара) 2.5 кг</t>
+          <t>Грунт-концентрат ВД-ВА Ореол Дисконт 3 кг</t>
         </is>
       </c>
       <c r="G167" s="30" t="n">
-        <v>70662</v>
+        <v>67654</v>
       </c>
       <c r="H167" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -7326,25 +7361,25 @@
       </c>
       <c r="D168" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E168" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F168" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" матовая серая 0.9 кг</t>
+          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 1 кг</t>
         </is>
       </c>
       <c r="G168" s="30" t="n">
-        <v>71787</v>
+        <v>65722</v>
       </c>
       <c r="H168" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7364,25 +7399,25 @@
       </c>
       <c r="D169" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E169" s="30" t="inlineStr">
         <is>
-          <t>Эмали ВДАК</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F169" s="30" t="inlineStr">
         <is>
-          <t>Эмаль акриловая "ОРЕОЛ" матовая чёрная 0.9 кг</t>
+          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 10 кг</t>
         </is>
       </c>
       <c r="G169" s="30" t="n">
-        <v>71790</v>
+        <v>65724</v>
       </c>
       <c r="H169" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7412,11 +7447,11 @@
       </c>
       <c r="F170" s="30" t="inlineStr">
         <is>
-          <t>Грунт-концентрат ВД-ВА Ореол Дисконт 1 кг</t>
+          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 5 кг</t>
         </is>
       </c>
       <c r="G170" s="30" t="n">
-        <v>4209</v>
+        <v>65723</v>
       </c>
       <c r="H170" s="17" t="inlineStr">
         <is>
@@ -7450,11 +7485,11 @@
       </c>
       <c r="F171" s="30" t="inlineStr">
         <is>
-          <t>Грунт-концентрат ВД-ВА Ореол Дисконт 3 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 1 кг</t>
         </is>
       </c>
       <c r="G171" s="30" t="n">
-        <v>67654</v>
+        <v>4484</v>
       </c>
       <c r="H171" s="17" t="inlineStr">
         <is>
@@ -7488,11 +7523,11 @@
       </c>
       <c r="F172" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 1 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 10 кг</t>
         </is>
       </c>
       <c r="G172" s="30" t="n">
-        <v>65722</v>
+        <v>4485</v>
       </c>
       <c r="H172" s="17" t="inlineStr">
         <is>
@@ -7526,11 +7561,11 @@
       </c>
       <c r="F173" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 10 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 5 кг</t>
         </is>
       </c>
       <c r="G173" s="30" t="n">
-        <v>65724</v>
+        <v>4487</v>
       </c>
       <c r="H173" s="17" t="inlineStr">
         <is>
@@ -7564,15 +7599,15 @@
       </c>
       <c r="F174" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ВД универсальная ОРЕОЛ ДИСКОНТ 5 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 1 кг</t>
         </is>
       </c>
       <c r="G174" s="30" t="n">
-        <v>65723</v>
+        <v>50649</v>
       </c>
       <c r="H174" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -7602,11 +7637,11 @@
       </c>
       <c r="F175" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 1 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 10 кг</t>
         </is>
       </c>
       <c r="G175" s="30" t="n">
-        <v>4484</v>
+        <v>50651</v>
       </c>
       <c r="H175" s="17" t="inlineStr">
         <is>
@@ -7640,11 +7675,11 @@
       </c>
       <c r="F176" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 10 кг</t>
+          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 5 кг</t>
         </is>
       </c>
       <c r="G176" s="30" t="n">
-        <v>4485</v>
+        <v>50650</v>
       </c>
       <c r="H176" s="17" t="inlineStr">
         <is>
@@ -7673,16 +7708,16 @@
       </c>
       <c r="E177" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F177" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения ВД ДИСКОНТ 5 кг</t>
+          <t>Краска ВД Ореол Дисконт для потолков супербелая 1.5 кг</t>
         </is>
       </c>
       <c r="G177" s="30" t="n">
-        <v>4487</v>
+        <v>5402</v>
       </c>
       <c r="H177" s="17" t="inlineStr">
         <is>
@@ -7711,20 +7746,20 @@
       </c>
       <c r="E178" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F178" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 1 кг</t>
+          <t>Краска ВД Ореол Дисконт для потолков супербелая 13 кг</t>
         </is>
       </c>
       <c r="G178" s="30" t="n">
-        <v>50649</v>
+        <v>5404</v>
       </c>
       <c r="H178" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7749,20 +7784,20 @@
       </c>
       <c r="E179" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F179" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 10 кг</t>
+          <t>Краска ВД Ореол Дисконт для потолков супербелая 3 кг</t>
         </is>
       </c>
       <c r="G179" s="30" t="n">
-        <v>50651</v>
+        <v>5409</v>
       </c>
       <c r="H179" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -7787,16 +7822,16 @@
       </c>
       <c r="E180" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Краски</t>
         </is>
       </c>
       <c r="F180" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ОРЕОЛ глубокого проникновения с антисептиком ВД ДИСКОНТ розовая 5 кг</t>
+          <t>Краска ВД Ореол Дисконт для потолков супербелая 6.5 кг</t>
         </is>
       </c>
       <c r="G180" s="30" t="n">
-        <v>50650</v>
+        <v>5412</v>
       </c>
       <c r="H180" s="17" t="inlineStr">
         <is>
@@ -7830,11 +7865,11 @@
       </c>
       <c r="F181" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для потолков супербелая 1.5 кг</t>
+          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 1.5 кг</t>
         </is>
       </c>
       <c r="G181" s="30" t="n">
-        <v>5402</v>
+        <v>5415</v>
       </c>
       <c r="H181" s="17" t="inlineStr">
         <is>
@@ -7868,11 +7903,11 @@
       </c>
       <c r="F182" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для потолков супербелая 13 кг</t>
+          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 13 кг</t>
         </is>
       </c>
       <c r="G182" s="30" t="n">
-        <v>5404</v>
+        <v>5417</v>
       </c>
       <c r="H182" s="17" t="inlineStr">
         <is>
@@ -7906,11 +7941,11 @@
       </c>
       <c r="F183" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для потолков супербелая 3 кг</t>
+          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 3 кг</t>
         </is>
       </c>
       <c r="G183" s="30" t="n">
-        <v>5409</v>
+        <v>5420</v>
       </c>
       <c r="H183" s="17" t="inlineStr">
         <is>
@@ -7944,11 +7979,11 @@
       </c>
       <c r="F184" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для потолков супербелая 6.5 кг</t>
+          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 6.5 кг</t>
         </is>
       </c>
       <c r="G184" s="30" t="n">
-        <v>5412</v>
+        <v>5422</v>
       </c>
       <c r="H184" s="17" t="inlineStr">
         <is>
@@ -7982,11 +8017,11 @@
       </c>
       <c r="F185" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 1.5 кг</t>
+          <t>Краска ВД Ореол Дисконт интерьерная 1.5 кг</t>
         </is>
       </c>
       <c r="G185" s="30" t="n">
-        <v>5415</v>
+        <v>5424</v>
       </c>
       <c r="H185" s="17" t="inlineStr">
         <is>
@@ -8020,11 +8055,11 @@
       </c>
       <c r="F186" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 13 кг</t>
+          <t>Краска ВД Ореол Дисконт интерьерная 13 кг</t>
         </is>
       </c>
       <c r="G186" s="30" t="n">
-        <v>5417</v>
+        <v>5426</v>
       </c>
       <c r="H186" s="17" t="inlineStr">
         <is>
@@ -8058,11 +8093,11 @@
       </c>
       <c r="F187" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 3 кг</t>
+          <t>Краска ВД Ореол Дисконт интерьерная 3 кг</t>
         </is>
       </c>
       <c r="G187" s="30" t="n">
-        <v>5420</v>
+        <v>5429</v>
       </c>
       <c r="H187" s="17" t="inlineStr">
         <is>
@@ -8096,11 +8131,11 @@
       </c>
       <c r="F188" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт для стен и потолков моющаяся 6.5 кг</t>
+          <t>Краска ВД Ореол Дисконт интерьерная 6.5 кг</t>
         </is>
       </c>
       <c r="G188" s="30" t="n">
-        <v>5422</v>
+        <v>5431</v>
       </c>
       <c r="H188" s="17" t="inlineStr">
         <is>
@@ -8134,11 +8169,11 @@
       </c>
       <c r="F189" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт интерьерная 1.5 кг</t>
+          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 1.5 кг</t>
         </is>
       </c>
       <c r="G189" s="30" t="n">
-        <v>5424</v>
+        <v>5433</v>
       </c>
       <c r="H189" s="17" t="inlineStr">
         <is>
@@ -8172,11 +8207,11 @@
       </c>
       <c r="F190" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт интерьерная 13 кг</t>
+          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 13 кг</t>
         </is>
       </c>
       <c r="G190" s="30" t="n">
-        <v>5426</v>
+        <v>5435</v>
       </c>
       <c r="H190" s="17" t="inlineStr">
         <is>
@@ -8210,11 +8245,11 @@
       </c>
       <c r="F191" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт интерьерная 3 кг</t>
+          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 3 кг</t>
         </is>
       </c>
       <c r="G191" s="30" t="n">
-        <v>5429</v>
+        <v>5438</v>
       </c>
       <c r="H191" s="17" t="inlineStr">
         <is>
@@ -8248,11 +8283,11 @@
       </c>
       <c r="F192" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт интерьерная 6.5 кг</t>
+          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 6.5 кг</t>
         </is>
       </c>
       <c r="G192" s="30" t="n">
-        <v>5431</v>
+        <v>5440</v>
       </c>
       <c r="H192" s="17" t="inlineStr">
         <is>
@@ -8269,14 +8304,14 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C193" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C193" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D193" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E193" s="30" t="inlineStr">
@@ -8286,15 +8321,15 @@
       </c>
       <c r="F193" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 1.5 кг</t>
+          <t>Краска интерьерная моющаяся AvantGarde (база А) матовая белая</t>
         </is>
       </c>
       <c r="G193" s="30" t="n">
-        <v>5433</v>
+        <v>0</v>
       </c>
       <c r="H193" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8307,14 +8342,14 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C194" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C194" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D194" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E194" s="30" t="inlineStr">
@@ -8324,15 +8359,15 @@
       </c>
       <c r="F194" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 13 кг</t>
+          <t>Краска интерьерная моющаяся AvantGarde (база С) матовая</t>
         </is>
       </c>
       <c r="G194" s="30" t="n">
-        <v>5435</v>
+        <v>0</v>
       </c>
       <c r="H194" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8345,32 +8380,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C195" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C195" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D195" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E195" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F195" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 3 кг</t>
+          <t>Грунт-концентрат АКВАСТОП ОРЕОЛ 1 кг</t>
         </is>
       </c>
       <c r="G195" s="30" t="n">
-        <v>5438</v>
+        <v>66403</v>
       </c>
       <c r="H195" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8383,32 +8418,32 @@
           <t>Помещения (интерьер)</t>
         </is>
       </c>
-      <c r="C196" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C196" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D196" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E196" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F196" s="30" t="inlineStr">
         <is>
-          <t>Краска ВД Ореол Дисконт фасадная атмосферостойкая 6.5 кг</t>
+          <t>Грунтовка бетон-контакт ОРЕОЛ 12 кг</t>
         </is>
       </c>
       <c r="G196" s="30" t="n">
-        <v>5440</v>
+        <v>66140</v>
       </c>
       <c r="H196" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8428,25 +8463,25 @@
       </c>
       <c r="D197" s="30" t="inlineStr">
         <is>
-          <t>AvantGarde</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E197" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F197" s="30" t="inlineStr">
         <is>
-          <t>Краска интерьерная моющаяся AvantGarde (база А) матовая белая</t>
+          <t>Грунтовка бетон-контакт ОРЕОЛ 3 кг</t>
         </is>
       </c>
       <c r="G197" s="30" t="n">
-        <v>0</v>
+        <v>66138</v>
       </c>
       <c r="H197" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -8466,25 +8501,25 @@
       </c>
       <c r="D198" s="30" t="inlineStr">
         <is>
-          <t>AvantGarde</t>
+          <t>Ореол</t>
         </is>
       </c>
       <c r="E198" s="30" t="inlineStr">
         <is>
-          <t>Краски</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F198" s="30" t="inlineStr">
         <is>
-          <t>Краска интерьерная моющаяся AvantGarde (база С) матовая</t>
+          <t>Грунтовка бетон-контакт ОРЕОЛ 6 кг</t>
         </is>
       </c>
       <c r="G198" s="30" t="n">
-        <v>0</v>
+        <v>66139</v>
       </c>
       <c r="H198" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -8509,16 +8544,16 @@
       </c>
       <c r="E199" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F199" s="30" t="inlineStr">
         <is>
-          <t>Грунт-концентрат АКВАСТОП ОРЕОЛ 1 кг</t>
+          <t>Шпатлевка для влажных помещений ОРЕОЛ  1.5 кг</t>
         </is>
       </c>
       <c r="G199" s="30" t="n">
-        <v>66403</v>
+        <v>66923</v>
       </c>
       <c r="H199" s="17" t="inlineStr">
         <is>
@@ -8547,16 +8582,16 @@
       </c>
       <c r="E200" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F200" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка бетон-контакт ОРЕОЛ 12 кг</t>
+          <t>Шпатлевка для влажных помещений ОРЕОЛ  4 кг</t>
         </is>
       </c>
       <c r="G200" s="30" t="n">
-        <v>66140</v>
+        <v>66924</v>
       </c>
       <c r="H200" s="17" t="inlineStr">
         <is>
@@ -8585,16 +8620,16 @@
       </c>
       <c r="E201" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F201" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка бетон-контакт ОРЕОЛ 3 кг</t>
+          <t>Шпатлевка интерьерная латексная ОРЕОЛ 1.5 кг</t>
         </is>
       </c>
       <c r="G201" s="30" t="n">
-        <v>66138</v>
+        <v>66526</v>
       </c>
       <c r="H201" s="17" t="inlineStr">
         <is>
@@ -8623,20 +8658,20 @@
       </c>
       <c r="E202" s="30" t="inlineStr">
         <is>
-          <t>Грунтовки</t>
+          <t>Шпатлёвки</t>
         </is>
       </c>
       <c r="F202" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка бетон-контакт ОРЕОЛ 6 кг</t>
+          <t>Шпатлевка интерьерная латексная ОРЕОЛ 4 кг</t>
         </is>
       </c>
       <c r="G202" s="30" t="n">
-        <v>66139</v>
+        <v>66527</v>
       </c>
       <c r="H202" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8666,15 +8701,15 @@
       </c>
       <c r="F203" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка для влажных помещений ОРЕОЛ  1.5 кг</t>
+          <t>Шпатлевка финишная ОРЕОЛ 1.5 кг</t>
         </is>
       </c>
       <c r="G203" s="30" t="n">
-        <v>66923</v>
+        <v>66524</v>
       </c>
       <c r="H203" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8704,15 +8739,15 @@
       </c>
       <c r="F204" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка для влажных помещений ОРЕОЛ  4 кг</t>
+          <t>Шпатлевка финишная ОРЕОЛ 4 кг</t>
         </is>
       </c>
       <c r="G204" s="30" t="n">
-        <v>66924</v>
+        <v>66525</v>
       </c>
       <c r="H204" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8767,7 @@
       </c>
       <c r="D205" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E205" s="30" t="inlineStr">
@@ -8742,15 +8777,15 @@
       </c>
       <c r="F205" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка интерьерная латексная ОРЕОЛ 1.5 кг</t>
+          <t>Шпатлевка ОРЕОЛ универсальная масляно-клеевая для внутренних работ ДИСКОНТ 1.5 кг</t>
         </is>
       </c>
       <c r="G205" s="30" t="n">
-        <v>66526</v>
+        <v>65828</v>
       </c>
       <c r="H205" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8805,7 @@
       </c>
       <c r="D206" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Ореол Дисконт</t>
         </is>
       </c>
       <c r="E206" s="30" t="inlineStr">
@@ -8780,15 +8815,15 @@
       </c>
       <c r="F206" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка интерьерная латексная ОРЕОЛ 4 кг</t>
+          <t>Шпатлевка ОРЕОЛ универсальная масляно-клеевая для внутренних работ ДИСКОНТ 3.5 кг</t>
         </is>
       </c>
       <c r="G206" s="30" t="n">
-        <v>66527</v>
+        <v>88947</v>
       </c>
       <c r="H206" s="17" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8808,21 +8843,21 @@
       </c>
       <c r="D207" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Простокрашено! БАУ</t>
         </is>
       </c>
       <c r="E207" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F207" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка финишная ОРЕОЛ 1.5 кг</t>
+          <t>Грунтовка ГФ-021 Простокрашено серая 2.5 кг</t>
         </is>
       </c>
       <c r="G207" s="30" t="n">
-        <v>66524</v>
+        <v>85161</v>
       </c>
       <c r="H207" s="17" t="inlineStr">
         <is>
@@ -8846,25 +8881,25 @@
       </c>
       <c r="D208" s="30" t="inlineStr">
         <is>
-          <t>Ореол</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E208" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F208" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка финишная ОРЕОЛ 4 кг</t>
+          <t>Грунтовка ГФ-021 Расцвет серая 2.2 кг</t>
         </is>
       </c>
       <c r="G208" s="30" t="n">
-        <v>66525</v>
+        <v>11202</v>
       </c>
       <c r="H208" s="17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -8884,25 +8919,25 @@
       </c>
       <c r="D209" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E209" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F209" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка ОРЕОЛ универсальная масляно-клеевая для внутренних работ ДИСКОНТ 1.5 кг</t>
+          <t>Грунтовка быстросохнущая ГФ-021 Расцвет красно-коричневая 2.5 кг</t>
         </is>
       </c>
       <c r="G209" s="30" t="n">
-        <v>65828</v>
+        <v>73562</v>
       </c>
       <c r="H209" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -8922,25 +8957,25 @@
       </c>
       <c r="D210" s="30" t="inlineStr">
         <is>
-          <t>Ореол Дисконт</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E210" s="30" t="inlineStr">
         <is>
-          <t>Шпатлёвки</t>
+          <t>Грунтовки</t>
         </is>
       </c>
       <c r="F210" s="30" t="inlineStr">
         <is>
-          <t>Шпатлевка ОРЕОЛ универсальная масляно-клеевая для внутренних работ ДИСКОНТ 3.5 кг</t>
+          <t>Грунтовка быстросохнущая ГФ-021 Расцвет серая 1 кг</t>
         </is>
       </c>
       <c r="G210" s="30" t="n">
-        <v>88947</v>
+        <v>73565</v>
       </c>
       <c r="H210" s="17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8995,7 @@
       </c>
       <c r="D211" s="30" t="inlineStr">
         <is>
-          <t>Простокрашено! БАУ</t>
+          <t>Расцвет</t>
         </is>
       </c>
       <c r="E211" s="30" t="inlineStr">
@@ -8970,11 +9005,11 @@
       </c>
       <c r="F211" s="30" t="inlineStr">
         <is>
-          <t>Грунтовка ГФ-021 Простокрашено серая 2.5 кг</t>
+          <t>Грунтовка быстросохнущая ГФ-021 Расцвет серая 2.5 кг</t>
         </is>
       </c>
       <c r="G211" s="30" t="n">
-        <v>85161</v>
+        <v>73566</v>
       </c>
       <c r="H211" s="17" t="inlineStr">
         <is>
@@ -8983,152 +9018,152 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="17" t="n">
+      <c r="A212" s="19" t="n">
         <v>209</v>
       </c>
-      <c r="B212" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C212" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D212" s="30" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E212" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовки</t>
-        </is>
-      </c>
-      <c r="F212" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовка ГФ-021 Расцвет серая 2.2 кг</t>
-        </is>
-      </c>
-      <c r="G212" s="30" t="n">
-        <v>11202</v>
-      </c>
-      <c r="H212" s="17" t="inlineStr">
-        <is>
-          <t>С</t>
+      <c r="B212" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C212" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D212" s="31" t="inlineStr">
+        <is>
+          <t>PROFIWOOD</t>
+        </is>
+      </c>
+      <c r="E212" s="31" t="inlineStr">
+        <is>
+          <t>Лаки</t>
+        </is>
+      </c>
+      <c r="F212" s="31" t="inlineStr">
+        <is>
+          <t>Лак по дереву и камню PROFIWOOD ВД глянцевый 0.9 кг</t>
+        </is>
+      </c>
+      <c r="G212" s="31" t="n">
+        <v>64974</v>
+      </c>
+      <c r="H212" s="19" t="inlineStr">
+        <is>
+          <t>В</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="17" t="n">
+      <c r="A213" s="19" t="n">
         <v>210</v>
       </c>
-      <c r="B213" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C213" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D213" s="30" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E213" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовки</t>
-        </is>
-      </c>
-      <c r="F213" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовка быстросохнущая ГФ-021 Расцвет красно-коричневая 2.5 кг</t>
-        </is>
-      </c>
-      <c r="G213" s="30" t="n">
-        <v>73562</v>
-      </c>
-      <c r="H213" s="17" t="inlineStr">
+      <c r="B213" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C213" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D213" s="31" t="inlineStr">
+        <is>
+          <t>PROFIWOOD</t>
+        </is>
+      </c>
+      <c r="E213" s="31" t="inlineStr">
+        <is>
+          <t>Лаки</t>
+        </is>
+      </c>
+      <c r="F213" s="31" t="inlineStr">
+        <is>
+          <t>Лак по дереву и камню PROFIWOOD ВД глянцевый 2.2 кг</t>
+        </is>
+      </c>
+      <c r="G213" s="31" t="n">
+        <v>64975</v>
+      </c>
+      <c r="H213" s="19" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="17" t="n">
+      <c r="A214" s="19" t="n">
         <v>211</v>
       </c>
-      <c r="B214" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C214" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D214" s="30" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E214" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовки</t>
-        </is>
-      </c>
-      <c r="F214" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовка быстросохнущая ГФ-021 Расцвет серая 1 кг</t>
-        </is>
-      </c>
-      <c r="G214" s="30" t="n">
-        <v>73565</v>
-      </c>
-      <c r="H214" s="17" t="inlineStr">
-        <is>
-          <t>В</t>
+      <c r="B214" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C214" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D214" s="31" t="inlineStr">
+        <is>
+          <t>PROFIWOOD</t>
+        </is>
+      </c>
+      <c r="E214" s="31" t="inlineStr">
+        <is>
+          <t>Лаки</t>
+        </is>
+      </c>
+      <c r="F214" s="31" t="inlineStr">
+        <is>
+          <t>Лак-антисептик для бань и саун PROFIWOOD ВД 0.9 кг</t>
+        </is>
+      </c>
+      <c r="G214" s="31" t="n">
+        <v>6493</v>
+      </c>
+      <c r="H214" s="19" t="inlineStr">
+        <is>
+          <t>А</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="17" t="n">
+      <c r="A215" s="19" t="n">
         <v>212</v>
       </c>
-      <c r="B215" s="30" t="inlineStr">
-        <is>
-          <t>Помещения (интерьер)</t>
-        </is>
-      </c>
-      <c r="C215" s="29" t="inlineStr">
-        <is>
-          <t>Органическая</t>
-        </is>
-      </c>
-      <c r="D215" s="30" t="inlineStr">
-        <is>
-          <t>Расцвет</t>
-        </is>
-      </c>
-      <c r="E215" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовки</t>
-        </is>
-      </c>
-      <c r="F215" s="30" t="inlineStr">
-        <is>
-          <t>Грунтовка быстросохнущая ГФ-021 Расцвет серая 2.5 кг</t>
-        </is>
-      </c>
-      <c r="G215" s="30" t="n">
-        <v>73566</v>
-      </c>
-      <c r="H215" s="17" t="inlineStr">
+      <c r="B215" s="31" t="inlineStr">
+        <is>
+          <t>Дерево</t>
+        </is>
+      </c>
+      <c r="C215" s="28" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная</t>
+        </is>
+      </c>
+      <c r="D215" s="31" t="inlineStr">
+        <is>
+          <t>PROFIWOOD</t>
+        </is>
+      </c>
+      <c r="E215" s="31" t="inlineStr">
+        <is>
+          <t>Лаки</t>
+        </is>
+      </c>
+      <c r="F215" s="31" t="inlineStr">
+        <is>
+          <t>Лак-антисептик для бань и саун PROFIWOOD ВД 2.5 кг</t>
+        </is>
+      </c>
+      <c r="G215" s="31" t="n">
+        <v>6494</v>
+      </c>
+      <c r="H215" s="19" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -9155,20 +9190,20 @@
       </c>
       <c r="E216" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Растворы для защиты древесины</t>
         </is>
       </c>
       <c r="F216" s="31" t="inlineStr">
         <is>
-          <t>Лак по дереву и камню PROFIWOOD ВД глянцевый 0.9 кг</t>
+          <t>Раствор водный защитного средства для древесины ФБС-255 10 л 10 кг</t>
         </is>
       </c>
       <c r="G216" s="31" t="n">
-        <v>64974</v>
+        <v>83757</v>
       </c>
       <c r="H216" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -9181,32 +9216,32 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C217" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C217" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D217" s="31" t="inlineStr">
         <is>
-          <t>PROFIWOOD</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E217" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F217" s="31" t="inlineStr">
         <is>
-          <t>Лак по дереву и камню PROFIWOOD ВД глянцевый 2.2 кг</t>
+          <t>Защитно-декоративное покрытие для дерева AvantGarde белое</t>
         </is>
       </c>
       <c r="G217" s="31" t="n">
-        <v>64975</v>
+        <v>0</v>
       </c>
       <c r="H217" s="19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9219,32 +9254,32 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C218" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C218" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D218" s="31" t="inlineStr">
         <is>
-          <t>PROFIWOOD</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E218" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F218" s="31" t="inlineStr">
         <is>
-          <t>Лак-антисептик для бань и саун PROFIWOOD ВД 0.9 кг</t>
+          <t>Защитно-декоративное покрытие для дерева AvantGarde олива</t>
         </is>
       </c>
       <c r="G218" s="31" t="n">
-        <v>6493</v>
+        <v>0</v>
       </c>
       <c r="H218" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9257,32 +9292,32 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C219" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C219" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D219" s="31" t="inlineStr">
         <is>
-          <t>PROFIWOOD</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E219" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F219" s="31" t="inlineStr">
         <is>
-          <t>Лак-антисептик для бань и саун PROFIWOOD ВД 2.5 кг</t>
+          <t>Защитно-декоративное покрытие для дерева AvantGarde сосна</t>
         </is>
       </c>
       <c r="G219" s="31" t="n">
-        <v>6494</v>
+        <v>0</v>
       </c>
       <c r="H219" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9295,32 +9330,32 @@
           <t>Дерево</t>
         </is>
       </c>
-      <c r="C220" s="28" t="inlineStr">
-        <is>
-          <t>Водно-дисперсионная</t>
+      <c r="C220" s="29" t="inlineStr">
+        <is>
+          <t>Органическая</t>
         </is>
       </c>
       <c r="D220" s="31" t="inlineStr">
         <is>
-          <t>PROFIWOOD</t>
+          <t>AvantGarde</t>
         </is>
       </c>
       <c r="E220" s="31" t="inlineStr">
         <is>
-          <t>Растворы для защиты древесины</t>
+          <t>Лаки</t>
         </is>
       </c>
       <c r="F220" s="31" t="inlineStr">
         <is>
-          <t>Раствор водный защитного средства для древесины ФБС-255 10 л 10 кг</t>
+          <t>Лак высокой твердости паркетный AvantGarde глянцевый бесцветный</t>
         </is>
       </c>
       <c r="G220" s="31" t="n">
-        <v>83757</v>
+        <v>0</v>
       </c>
       <c r="H220" s="19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>С</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9380,12 @@
       </c>
       <c r="E221" s="31" t="inlineStr">
         <is>
-          <t>Декоративные составы</t>
+          <t>Лаки</t>
         </is>
       </c>
       <c r="F221" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для дерева AvantGarde белое</t>
+          <t>Лак высокой твердости паркетный AvantGarde полуматовый бесцветный</t>
         </is>
       </c>
       <c r="G221" s="31" t="n">
@@ -9383,12 +9418,12 @@
       </c>
       <c r="E222" s="31" t="inlineStr">
         <is>
-          <t>Декоративные составы</t>
+          <t>Лаки</t>
         </is>
       </c>
       <c r="F222" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для дерева AvantGarde олива</t>
+          <t>Лак высокой твердости яхтный AvantGarde глянцевый бесцветный</t>
         </is>
       </c>
       <c r="G222" s="31" t="n">
@@ -9421,12 +9456,12 @@
       </c>
       <c r="E223" s="31" t="inlineStr">
         <is>
-          <t>Декоративные составы</t>
+          <t>Лаки</t>
         </is>
       </c>
       <c r="F223" s="31" t="inlineStr">
         <is>
-          <t>Защитно-декоративное покрытие для дерева AvantGarde сосна</t>
+          <t>Лак высокой твердости яхтный AvantGarde полуматовый бесцветный</t>
         </is>
       </c>
       <c r="G223" s="31" t="n">
@@ -9454,25 +9489,25 @@
       </c>
       <c r="D224" s="31" t="inlineStr">
         <is>
-          <t>AvantGarde</t>
+          <t>PROFIWOOD</t>
         </is>
       </c>
       <c r="E224" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F224" s="31" t="inlineStr">
         <is>
-          <t>Лак высокой твердости паркетный AvantGarde глянцевый бесцветный</t>
+          <t>Антисептик кроющий PROFIWOOD бежевый 0.8 л 1 кг</t>
         </is>
       </c>
       <c r="G224" s="31" t="n">
-        <v>0</v>
+        <v>88845</v>
       </c>
       <c r="H224" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -9492,25 +9527,25 @@
       </c>
       <c r="D225" s="31" t="inlineStr">
         <is>
-          <t>AvantGarde</t>
+          <t>PROFIWOOD</t>
         </is>
       </c>
       <c r="E225" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F225" s="31" t="inlineStr">
         <is>
-          <t>Лак высокой твердости паркетный AvantGarde полуматовый бесцветный</t>
+          <t>Антисептик кроющий PROFIWOOD бежевый 2.4 л 3 кг</t>
         </is>
       </c>
       <c r="G225" s="31" t="n">
-        <v>0</v>
+        <v>88846</v>
       </c>
       <c r="H225" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -9530,25 +9565,25 @@
       </c>
       <c r="D226" s="31" t="inlineStr">
         <is>
-          <t>AvantGarde</t>
+          <t>PROFIWOOD</t>
         </is>
       </c>
       <c r="E226" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F226" s="31" t="inlineStr">
         <is>
-          <t>Лак высокой твердости яхтный AvantGarde глянцевый бесцветный</t>
+          <t>Антисептик кроющий PROFIWOOD скандинавский серый 0.8 л 1 кг</t>
         </is>
       </c>
       <c r="G226" s="31" t="n">
-        <v>0</v>
+        <v>88849</v>
       </c>
       <c r="H226" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -9568,25 +9603,25 @@
       </c>
       <c r="D227" s="31" t="inlineStr">
         <is>
-          <t>AvantGarde</t>
+          <t>PROFIWOOD</t>
         </is>
       </c>
       <c r="E227" s="31" t="inlineStr">
         <is>
-          <t>Лаки</t>
+          <t>Декоративные составы</t>
         </is>
       </c>
       <c r="F227" s="31" t="inlineStr">
         <is>
-          <t>Лак высокой твердости яхтный AvantGarde полуматовый бесцветный</t>
+          <t>Антисептик кроющий PROFIWOOD скандинавский серый 2.4 л 3 кг</t>
         </is>
       </c>
       <c r="G227" s="31" t="n">
-        <v>0</v>
+        <v>88851</v>
       </c>
       <c r="H227" s="19" t="inlineStr">
         <is>
-          <t>С</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -12549,15 +12584,15 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>6</v>
@@ -12575,22 +12610,22 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
         <v>19</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F5" s="30" t="inlineStr">
         <is>
-          <t>Краски интерьерные, шпатлёвки, грунтовки — стены, потолки</t>
+          <t>Краски интерьерные, OSB, шпатлёвки, грунтовки, резиновая — стены, потолки</t>
         </is>
       </c>
     </row>
@@ -12601,22 +12636,22 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="D6" s="19" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E6" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F6" s="31" t="inlineStr">
         <is>
-          <t>Лаки, пропитки, антисептики, защитно-декоративные — окна, двери, террасы</t>
+          <t>Лаки, пропитки, антисептики PROFIWOOD, защитно-декоративные — окна, двери, террасы</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12703,7 @@
       </c>
       <c r="F8" s="33" t="inlineStr">
         <is>
-          <t>Краски фасадные ВД — наружные стены зданий (NEWTONE, AvantGarde)</t>
+          <t>Краски фасадные ВД (NEWTONE, AvantGarde) — наружные стены</t>
         </is>
       </c>
     </row>
@@ -12687,10 +12722,10 @@
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F9" s="34" t="n"/>
     </row>
